--- a/DICIONARIO DE DADOS.xlsx
+++ b/DICIONARIO DE DADOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e100e31f92dca133/Documentos/sql-migracao-main/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0-Repositorios\sql-migracao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="533" documentId="13_ncr:1_{A5893538-FCB4-4A40-A055-475EFFABA56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2873E8C-E7EB-4B02-93E7-62F23A332FE9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410C7918-B35C-48D0-9175-FFB6C19CE284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="920" xr2:uid="{365E4779-0F30-4366-ADA5-894CEE121BCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="920" firstSheet="1" activeTab="6" xr2:uid="{365E4779-0F30-4366-ADA5-894CEE121BCE}"/>
   </bookViews>
   <sheets>
     <sheet name="ALT CADASTRAIS" sheetId="12" r:id="rId1"/>
@@ -54,6 +54,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -101,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2323" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="858">
   <si>
     <t>TM</t>
   </si>
@@ -3248,6 +3251,9 @@
   </si>
   <si>
     <t>VALOR</t>
+  </si>
+  <si>
+    <t>CODSECAO</t>
   </si>
 </sst>
 </file>
@@ -3734,10 +3740,10 @@
   <autoFilter ref="A1:E11" xr:uid="{8C310D2C-F6B4-4932-9C52-9C6BC6E69EA9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{49BB2A88-A90B-4353-A37E-64AE14BD9B2D}" uniqueName="1" name="TM" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{04D56926-9996-463D-961B-B0FDEBE4CCBE}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{6BC0D58C-7B16-490B-8F47-82E8B71CF566}" uniqueName="3" name="D" queryTableFieldId="3" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{B30BA9C1-3153-4150-8DC9-D12136937161}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{7C491190-2553-4FD7-8B2F-E1B94C652546}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{04D56926-9996-463D-961B-B0FDEBE4CCBE}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{6BC0D58C-7B16-490B-8F47-82E8B71CF566}" uniqueName="3" name="D" queryTableFieldId="3" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{B30BA9C1-3153-4150-8DC9-D12136937161}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{7C491190-2553-4FD7-8B2F-E1B94C652546}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3776,10 +3782,10 @@
   <autoFilter ref="A1:E30" xr:uid="{28DBD394-A0D6-4BD4-9D64-1910F4191797}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A30736FA-8E41-4970-BE06-D57D2619DC1B}" uniqueName="1" name="TM" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{D9A2309B-9158-49DF-B8FB-CEBF1D8C2255}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{D9A2309B-9158-49DF-B8FB-CEBF1D8C2255}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="36"/>
     <tableColumn id="3" xr3:uid="{B9B0276C-ACC4-4F21-9065-5455D51A346D}" uniqueName="3" name="D" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{94831E57-E2A9-4973-AD26-AAF75A94B34E}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{D8437505-26A2-4A17-A19C-88030BB9E7D3}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{94831E57-E2A9-4973-AD26-AAF75A94B34E}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{D8437505-26A2-4A17-A19C-88030BB9E7D3}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3796,10 +3802,10 @@
   </autoFilter>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C78C8D69-9EAC-4947-92B7-1466FB521E04}" uniqueName="1" name="TM" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{6F4AD0D7-6934-4460-9579-D26C1E27645D}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{723A5294-B050-48FD-8962-AF07E0F86152}" uniqueName="3" name="D" queryTableFieldId="3" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{F2130AD4-23D5-4BAD-886D-98BDC7525F48}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{9A5B0C1C-305C-4C2D-ACA5-B90A6A1D6808}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{6F4AD0D7-6934-4460-9579-D26C1E27645D}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{723A5294-B050-48FD-8962-AF07E0F86152}" uniqueName="3" name="D" queryTableFieldId="3" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{F2130AD4-23D5-4BAD-886D-98BDC7525F48}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{9A5B0C1C-305C-4C2D-ACA5-B90A6A1D6808}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3816,10 +3822,10 @@
   </autoFilter>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{08114E72-8165-43DC-9075-D32B6E22CEB2}" uniqueName="1" name="TM" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{F7082ECF-8E7D-49B5-96A0-F6AE1E10F65E}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{1FEAEDE5-C7D0-4B6C-9446-73D76CE45F4A}" uniqueName="3" name="D" queryTableFieldId="3" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{C1AFB090-35C7-4A32-B398-4E5A587F6651}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{90D200AD-A556-4E7F-B2CA-A1F5A788C5CF}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{F7082ECF-8E7D-49B5-96A0-F6AE1E10F65E}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{1FEAEDE5-C7D0-4B6C-9446-73D76CE45F4A}" uniqueName="3" name="D" queryTableFieldId="3" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{C1AFB090-35C7-4A32-B398-4E5A587F6651}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{90D200AD-A556-4E7F-B2CA-A1F5A788C5CF}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3830,10 +3836,10 @@
   <autoFilter ref="A1:E88" xr:uid="{7DB7ADD1-F422-4D18-9E8E-CC9EAF0740BA}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{E79E4592-2C33-4B2B-B3BA-5B1FB70A7050}" uniqueName="1" name="TM" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{0617077E-2B74-44C9-B926-F7DE66E92A95}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{002F0EFC-812C-4DAB-910B-ECBC14224E8A}" uniqueName="3" name="D" queryTableFieldId="3" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{455E5045-E9E6-4BC1-8ED4-EB8FB3C6AD10}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{258895DC-DE79-4F04-A07E-65D2A369E96E}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{0617077E-2B74-44C9-B926-F7DE66E92A95}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{002F0EFC-812C-4DAB-910B-ECBC14224E8A}" uniqueName="3" name="D" queryTableFieldId="3" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{455E5045-E9E6-4BC1-8ED4-EB8FB3C6AD10}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{258895DC-DE79-4F04-A07E-65D2A369E96E}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3844,10 +3850,10 @@
   <autoFilter ref="A1:E6" xr:uid="{9127BB2D-6DA6-46BB-A245-78B54E8CCB69}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{6CA3F6F3-29B9-4373-9AD9-60BF72D66A08}" uniqueName="1" name="TM" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{4245B475-E606-4028-8DAD-9D735E7A14B4}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{8500CF19-72D7-483E-A8A0-19FC770A2C19}" uniqueName="3" name="D" queryTableFieldId="3" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{26A31B4A-1BDC-4407-AF1B-1C5AF3CAA1B9}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{F3DABFCA-E344-4DEA-AE0D-824D1FED31CF}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{4245B475-E606-4028-8DAD-9D735E7A14B4}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{8500CF19-72D7-483E-A8A0-19FC770A2C19}" uniqueName="3" name="D" queryTableFieldId="3" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{26A31B4A-1BDC-4407-AF1B-1C5AF3CAA1B9}" uniqueName="4" name="OBR." queryTableFieldId="4" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{F3DABFCA-E344-4DEA-AE0D-824D1FED31CF}" uniqueName="5" name="DESCRIÇÃO" queryTableFieldId="5" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3902,9 +3908,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3942,7 +3948,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4048,7 +4054,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4190,7 +4196,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4202,16 +4208,16 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4240,7 +4246,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -4265,7 +4271,7 @@
         <v>LEFT(CAST(. AS ), 4) AS [Código da Unidade, cfe. Tabela de Unidades],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -4282,7 +4288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8</v>
       </c>
@@ -4299,7 +4305,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4316,7 +4322,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -4330,7 +4336,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>7</v>
       </c>
@@ -4344,7 +4350,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4361,7 +4367,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>40</v>
       </c>
@@ -4378,7 +4384,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4395,7 +4401,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>40</v>
       </c>
@@ -4426,21 +4432,21 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J144"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4472,7 +4478,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -4499,11 +4505,11 @@
         <v>783</v>
       </c>
       <c r="J2" t="str">
-        <f t="shared" ref="J2:J4" si="0">"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
+        <f t="shared" ref="J2:J5" si="0">"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
         <v>LEFT(CAST(PFUNC.CODCOLIGADA AS VARCHAR), 4) AS [Código da Empresa, cfe. Tabela de Empresas],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4</v>
       </c>
@@ -4520,12 +4526,18 @@
         <f t="shared" ref="F3:F66" si="1">"["&amp;E3&amp;"]"</f>
         <v>[Código do Estabelecimento Atual, cfe. Tabela de Estabelecimentos]</v>
       </c>
+      <c r="H3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I3" t="s">
+        <v>784</v>
+      </c>
       <c r="J3" t="str">
-        <f>"'' AS "&amp;F3&amp;","</f>
-        <v>'' AS [Código do Estabelecimento Atual, cfe. Tabela de Estabelecimentos],</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>LEFT(CAST(PFUNC.CODFILIAL AS ), 4) AS [Código do Estabelecimento Atual, cfe. Tabela de Estabelecimentos],</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
@@ -4549,14 +4561,14 @@
         <v>379</v>
       </c>
       <c r="I4" t="s">
-        <v>784</v>
+        <v>857</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>LEFT(CAST(PFUNC.CODFILIAL AS VARCHAR), 4) AS [Código da Unidade, cfe. Tabela de Unidades],</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>LEFT(CAST(PFUNC.CODSECAO AS VARCHAR), 4) AS [Código da Unidade, cfe. Tabela de Unidades],</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>8</v>
       </c>
@@ -4573,12 +4585,21 @@
         <f t="shared" si="1"/>
         <v>[Código do Contrato]</v>
       </c>
+      <c r="G5" t="s">
+        <v>335</v>
+      </c>
+      <c r="H5" t="s">
+        <v>379</v>
+      </c>
+      <c r="I5" t="s">
+        <v>851</v>
+      </c>
       <c r="J5" t="str">
-        <f>"'' AS "&amp;F5&amp;","</f>
-        <v>'' AS [Código do Contrato],</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>LEFT(CAST(PFUNC.CHAPA AS INTEGER), 8) AS [Código do Contrato],</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8</v>
       </c>
@@ -4609,7 +4630,7 @@
         <v>LEFT(CAST(PFUNC.CODPESSOA AS INTEGER), 8) AS [Código da Pessoa, cfe. Tabela de Pessoas],</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4640,7 +4661,7 @@
         <v>LEFT(CAST(PFUNC.CODSITUACAO AS VARCHAR), 1) AS [Situação:],</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -4659,7 +4680,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [1 – Ativo],</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -4678,7 +4699,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [2 – Afastado],</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>7</v>
       </c>
@@ -4697,7 +4718,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [3 – Rescindido no Mês],</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -4716,7 +4737,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [4 – Rescindido em Meses Anteriores],</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -4747,7 +4768,7 @@
         <v>LEFT(CAST(PFUNC.DATAADMISSAO AS DATE), 8) AS [Data de Admissão],</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
@@ -4778,7 +4799,7 @@
         <v>LEFT(CAST(PFUNC.CODRECEBIMENTO AS VARCHAR), 1) AS [Tipo de Salário:],</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>7</v>
       </c>
@@ -4793,7 +4814,7 @@
         <v>[1 – Mensal]</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>7</v>
       </c>
@@ -4808,7 +4829,7 @@
         <v>[2 – Por Quinzena]</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>7</v>
       </c>
@@ -4823,7 +4844,7 @@
         <v>[3 – Por Semana]</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>7</v>
       </c>
@@ -4838,7 +4859,7 @@
         <v>[4 – Por Dia]</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>7</v>
       </c>
@@ -4853,7 +4874,7 @@
         <v>[5 – Por Hora]</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>7</v>
       </c>
@@ -4868,7 +4889,7 @@
         <v>[6 – Por Tarefa]</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>7</v>
       </c>
@@ -4883,7 +4904,7 @@
         <v>[7 – Outros]</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>11</v>
       </c>
@@ -4908,7 +4929,7 @@
         <v>'' AS [Salário Contratual, cfe. Tipo de Salário],</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>5</v>
       </c>
@@ -4935,7 +4956,7 @@
 de Horistas (Tipo de Salário “5”).],</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>5</v>
       </c>
@@ -4960,7 +4981,7 @@
         <v>'' AS [Percentual de Insalubridade],</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>5</v>
       </c>
@@ -4985,7 +5006,7 @@
         <v>'' AS [Percentual de Periculosidade],</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2</v>
       </c>
@@ -5007,7 +5028,7 @@
         <v>'' AS [Nível de Exposição a Agente Nocivo:],</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>7</v>
       </c>
@@ -5026,7 +5047,7 @@
         <v>'' AS [00 – Nunca esteve exposto],</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>7</v>
       </c>
@@ -5045,7 +5066,7 @@
         <v>'' AS [01 – Não exposto, mas já esteve],</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>7</v>
       </c>
@@ -5064,7 +5085,7 @@
         <v>'' AS [02 – Exposto com aposentadoria aos 15 anos],</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>7</v>
       </c>
@@ -5083,7 +5104,7 @@
         <v>'' AS [03 – Exposto com aposentadoria aos 20 anos],</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>7</v>
       </c>
@@ -5102,7 +5123,7 @@
         <v>'' AS [04 – Exposto com aposentadoria aos 25 anos],</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>7</v>
       </c>
@@ -5121,7 +5142,7 @@
         <v>'' AS [05 – Não exposto com mais de um vínculo],</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>7</v>
       </c>
@@ -5140,7 +5161,7 @@
         <v>'' AS [06 – Exposto c/aposentadoria 15 anos e mais de um vínculo],</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>7</v>
       </c>
@@ -5159,7 +5180,7 @@
         <v>'' AS [07 – Exposto c/aposentadoria 20 anos e mais de um vínculo],</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>7</v>
       </c>
@@ -5178,7 +5199,7 @@
         <v>'' AS [08 – Exposto c/aposentadoria 25 anos e mais de um vínculo],</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5209,7 +5230,7 @@
         <v>LEFT(CAST(PFUNC.CODBANCOPAGTO AS INTEGER), 3) AS [Número do Banco do Funcionário (Banco Central)],</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>4</v>
       </c>
@@ -5240,7 +5261,7 @@
         <v>LEFT(CAST(PFUNC.CODAGENCIAPAGTO AS INTEGER), 4) AS [Agencia Bancária do Funcionário],</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1</v>
       </c>
@@ -5271,7 +5292,7 @@
         <v>LEFT(CAST(PFUNC.CODAGENCIAPAGTO AS INTEGER), 1) AS [Dígito da Agência Bancária do Funcionário],</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>15</v>
       </c>
@@ -5302,7 +5323,7 @@
         <v>LEFT(CAST(PFUNC.CONTAPAGAMENTO AS VARCHAR), 15) AS [Número/Dígito da Conta Corrente],</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>11</v>
       </c>
@@ -5324,7 +5345,7 @@
         <v>'' AS [Cadastro do Empregado na CEF (para o FGTS)],</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>8</v>
       </c>
@@ -5346,7 +5367,7 @@
         <v>'' AS [Data de Início do Contrato de Experiência/Temporário],</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>8</v>
       </c>
@@ -5368,7 +5389,7 @@
         <v>'' AS [Data de Término do Contrato de Experiência/Temporário],</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>4</v>
       </c>
@@ -5390,7 +5411,7 @@
         <v>'' AS [Número de Dias do Contrato de Experiência/Temporário],</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>8</v>
       </c>
@@ -5412,7 +5433,7 @@
         <v>'' AS [Data de Início da Prorrogação do Contrato de Experiência],</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>8</v>
       </c>
@@ -5434,7 +5455,7 @@
         <v>'' AS [Data de Término da Prorrogação do Contrato de Experiência],</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>4</v>
       </c>
@@ -5456,7 +5477,7 @@
         <v>'' AS [Número de Dias da Prorrogação do Contrato de Experiência],</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>8</v>
       </c>
@@ -5487,7 +5508,7 @@
         <v>LEFT(CAST(PFUNC.DATADEMISSA AS DATE), 8) AS [Data da Rescisão],</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>8</v>
       </c>
@@ -5509,7 +5530,7 @@
         <v>'' AS [Código do Cargo, cfe. Tabela de Cargos],</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>30</v>
       </c>
@@ -5540,7 +5561,7 @@
         <v>LEFT(CAST(PFUNC.MATRICULAESOCIAL AS VARCHAR), 30) AS [Matrícula para o eSocial],</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>1</v>
       </c>
@@ -5562,7 +5583,7 @@
         <v>2 AS [Tipo de Contrato],</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>7</v>
       </c>
@@ -5581,7 +5602,7 @@
         <v>'' AS [1 - Determinado],</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>7</v>
       </c>
@@ -5600,7 +5621,7 @@
         <v>'' AS [2 - Efetivo],</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>8</v>
       </c>
@@ -5622,7 +5643,7 @@
         <v>'' AS [Motivo de Rescisão Darwin],</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>7</v>
       </c>
@@ -5637,7 +5658,7 @@
         <v>[001 – Demissão com Justa Causa]</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>7</v>
       </c>
@@ -5652,7 +5673,7 @@
         <v>[002 – Demissão Sem Justa Causa]</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>7</v>
       </c>
@@ -5667,7 +5688,7 @@
         <v>[003 – Pedido de Demissão Sem Justa Causa]</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>7</v>
       </c>
@@ -5682,7 +5703,7 @@
         <v>[005 – Rescisão Por Término de Contrato Prazo Determinado]</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>7</v>
       </c>
@@ -5697,7 +5718,7 @@
         <v>[006 – Resc. Ant. do Contr. Por Prazo Determinado p/Empregado]</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>7</v>
       </c>
@@ -5712,7 +5733,7 @@
         <v>[007 – Resc. Ant. do Contr. Por Prazo Determinado p/Empresa]</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>7</v>
       </c>
@@ -5727,7 +5748,7 @@
         <v>[008 – Rescisão p/Término de Contr. Temporário]</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>7</v>
       </c>
@@ -5742,7 +5763,7 @@
         <v>[009 – Rescisão por Dispensa Indireta]</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>7</v>
       </c>
@@ -5757,7 +5778,7 @@
         <v>[010 – Rescisão por Culpa Recíproca]</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>7</v>
       </c>
@@ -5772,7 +5793,7 @@
         <v>[011 – Transferência de Estab. c/Ônus p/Cedente]</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>7</v>
       </c>
@@ -5787,7 +5808,7 @@
         <v>[012 – Transferência de Estab. s/Ônus p/Cedente]</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>7</v>
       </c>
@@ -5802,7 +5823,7 @@
         <v>[013 – Mudança de Regime Trabalhista]</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>7</v>
       </c>
@@ -5817,7 +5838,7 @@
         <v>[014 – Reforma de Militar]</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>7</v>
       </c>
@@ -5832,7 +5853,7 @@
         <v>[015 – Demissão sem Justa Causa Empr. Doméstico]</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>7</v>
       </c>
@@ -5847,7 +5868,7 @@
         <v>[016 – Rescisão por Acordo Entre as Partes]</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>7</v>
       </c>
@@ -5862,7 +5883,7 @@
         <v>[017 – Desligamento p/Tranf. Outro Sistema]</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>7</v>
       </c>
@@ -5877,7 +5898,7 @@
         <v>[020 – Falecimento]</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>7</v>
       </c>
@@ -5892,7 +5913,7 @@
         <v>[021 – Falecimento Decorr. de Acidente do Trabalho]</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>7</v>
       </c>
@@ -5907,7 +5928,7 @@
         <v>[022 – Falecimento Decorr. de Doença Pr.]</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>7</v>
       </c>
@@ -5922,7 +5943,7 @@
         <v>[023 – Falecimento Decorr. de Acidente no Trajeto]</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>7</v>
       </c>
@@ -5937,7 +5958,7 @@
         <v>[030 – Aposentadoria por Tempo de Serviço]</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>7</v>
       </c>
@@ -5952,7 +5973,7 @@
         <v>[031 – Aposentadoria por Idade]</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>7</v>
       </c>
@@ -5967,7 +5988,7 @@
         <v>[032 – Aposentadoria por Invalidez]</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>7</v>
       </c>
@@ -5982,7 +6003,7 @@
         <v>[033 – Aposentadoria p/Invalidez Dec.Acid.Trab.]</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>7</v>
       </c>
@@ -5997,7 +6018,7 @@
         <v>[034 – Aposentadoria p/Invalidez Dec.Doença Pr.]</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>7</v>
       </c>
@@ -6012,7 +6033,7 @@
         <v>[035 - Aposentadoria Compulsória]</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>7</v>
       </c>
@@ -6027,7 +6048,7 @@
         <v>[036 - Aposentadoria Especial]</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>7</v>
       </c>
@@ -6042,7 +6063,7 @@
         <v>[037 - Termino de Contrato - Estagiário]</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>7</v>
       </c>
@@ -6057,7 +6078,7 @@
         <v>[040 - Posse em outro Cargo Inacumulável]</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>7</v>
       </c>
@@ -6072,7 +6093,7 @@
         <v>[041 - Rescisão determinada pela Justiça]</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>7</v>
       </c>
@@ -6087,7 +6108,7 @@
         <v>[043 - Rescisão por Nulidade do Contrato Trab.]</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>7</v>
       </c>
@@ -6102,7 +6123,7 @@
         <v>[044 - Exoneração Diretor Não Empreg. s/J Causa]</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>7</v>
       </c>
@@ -6117,7 +6138,7 @@
         <v>[045 - Término de Mandato do Diretor Não Empreg]</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>7</v>
       </c>
@@ -6132,7 +6153,7 @@
         <v>[046 - Exoneração a pedido de Diretor Não Empr.]</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>7</v>
       </c>
@@ -6147,7 +6168,7 @@
         <v>[047 - Exoneração Diretor Não Empreg. Culpa Rec]</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>7</v>
       </c>
@@ -6162,7 +6183,7 @@
         <v>[048 - Morte do Diretor Não Empregado]</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>7</v>
       </c>
@@ -6177,7 +6198,7 @@
         <v>[049 - Exoneração Diretor Não Empregado p/Falên]</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>7</v>
       </c>
@@ -6192,7 +6213,7 @@
         <v>[1401 - Aprendiz - Término de Contrato]</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>7</v>
       </c>
@@ -6207,7 +6228,7 @@
         <v>[1402 - Aprendiz - Implemento da Idade]</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>7</v>
       </c>
@@ -6222,7 +6243,7 @@
         <v>[1403 - Aprendiz - Desemp. Insuf. ou Inadaptação]</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>7</v>
       </c>
@@ -6237,7 +6258,7 @@
         <v>[1404 - Aprendiz - Falta Disciplinar Grave]</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>7</v>
       </c>
@@ -6252,7 +6273,7 @@
         <v>[1405 - Aprendiz - Ausência Injustific. à Escola]</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>7</v>
       </c>
@@ -6267,7 +6288,7 @@
         <v>[1406 - Aprendiz - A Pedido do Aprendiz]</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>7</v>
       </c>
@@ -6282,7 +6303,7 @@
         <v>[1407 - Aprendiz - Fechamento da Empresa]</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>7</v>
       </c>
@@ -6297,7 +6318,7 @@
         <v>[9999 - Outros Motivos de Rescisão]</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>8</v>
       </c>
@@ -6328,7 +6349,7 @@
         <v>LEFT(CAST(PFUNC.CODCATEGORIAESOCIAL AS VARCHAR), 8) AS [Vínculo Empregatício:],</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E99" t="s">
         <v>349</v>
       </c>
@@ -6341,7 +6362,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [001-CLT - Empregador Pessoa Jurídica, categoria e-Social 101 - Empregado],</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>7</v>
       </c>
@@ -6362,7 +6383,7 @@
 contratado pela CLT],</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>7</v>
       </c>
@@ -6381,7 +6402,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [002 -Aprendiz, categoria e-Social 103 - Empregado – Aprendiz],</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>7</v>
       </c>
@@ -6402,7 +6423,7 @@
 Contrato de trabalho intermitenteIntermitente,categoriae-Social111-Empregado-],</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>7</v>
       </c>
@@ -6421,7 +6442,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [004 -Estagiário, categoria e-Social 901 - Estagiário],</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>7</v>
       </c>
@@ -6440,7 +6461,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [006-TrabalhadorTemporário-Lei6.019,categoriae-Social106-],</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E105" t="s">
         <v>355</v>
       </c>
@@ -6453,7 +6474,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [Trabalhador Temporário - contrato nos termos da Lei 6.019/74],</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>7</v>
       </c>
@@ -6472,7 +6493,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [007-TrabalhadorTemporário-Lei9.601,categoriae-Social105-],</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E107" t="s">
         <v>357</v>
       </c>
@@ -6485,7 +6506,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [Empregado – contrato a termo firmado nos termos da Lei 9601/98],</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E108" t="s">
         <v>358</v>
       </c>
@@ -6498,7 +6519,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [008 - CLT - Prazo Determinado Fixo ou Obra Certa, categoria e-Social 101 -],</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>7</v>
       </c>
@@ -6519,7 +6540,7 @@
 ou indireta contratado pela CLT],</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E110" t="s">
         <v>360</v>
       </c>
@@ -6532,7 +6553,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [009 - Trabalhador Rural - Empregador Pessoa Jurídica, categoria e-Social],</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>7</v>
       </c>
@@ -6553,7 +6574,7 @@
 direta ou indireta contratado pela CLT],</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>7</v>
       </c>
@@ -6576,7 +6597,7 @@
 ou indireta contratado pela CLT],</v>
       </c>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>7</v>
       </c>
@@ -6599,7 +6620,7 @@
 - sem acordo para antecipação mensal da multa rescisória do FGTSdeTrabalhoVerdeeAmarelosemMultaFGTSMensal,],</v>
       </c>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>7</v>
       </c>
@@ -6622,7 +6643,7 @@
 - com acordo para antecipação mensal da multa rescisória do FGTSdeTrabalhoVerdeeAmarelocomMultaFGTSMensal,],</v>
       </c>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>7</v>
       </c>
@@ -6643,7 +6664,7 @@
 Avulso PortuárioAvulsoPortuário, categoria e-Social 201 -Trabalhador],</v>
       </c>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>7</v>
       </c>
@@ -6664,7 +6685,7 @@
 Trabalhador Avulso Não PortuárioAvulsoNãoPortuário,categoriae-Social202-],</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>7</v>
       </c>
@@ -6687,7 +6708,7 @@
 fiscal],</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>7</v>
       </c>
@@ -6706,7 +6727,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [102 - Diretor com FGTS - Sócio, categoria do e-Social 723 - Contribuinte],</v>
       </c>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E119" t="s">
         <v>369</v>
       </c>
@@ -6719,7 +6740,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [individual – empresários, sócios e membro de conselho de administração ou],</v>
       </c>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E120" t="s">
         <v>370</v>
       </c>
@@ -6732,7 +6753,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [fiscal],</v>
       </c>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>7</v>
       </c>
@@ -6751,7 +6772,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [103 - Diretor sem FGTS - Não Sócio, categoria e-social 722 - Contribuinte],</v>
       </c>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E122" t="s">
         <v>372</v>
       </c>
@@ -6764,7 +6785,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [individual – Diretor não empregado, sem FGTS],</v>
       </c>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>7</v>
       </c>
@@ -6783,7 +6804,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [104 - Diretor com FGTS - Não Sócio, categoria e-Social 721 - Contribuinte],</v>
       </c>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E124" t="s">
         <v>374</v>
       </c>
@@ -6796,7 +6817,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [individual – Diretor não empregado, com FGTS],</v>
       </c>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>7</v>
       </c>
@@ -6815,7 +6836,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [201-Autônomo,categoriae-Social701-Contribuinteindividual–],</v>
       </c>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E126" t="s">
         <v>376</v>
       </c>
@@ -6830,7 +6851,7 @@
 de contribuinte individual],</v>
       </c>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E127" t="s">
         <v>377</v>
       </c>
@@ -6843,7 +6864,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [202-Freteiro-Carga,categoriae-Social712-Contribuinteindividual–],</v>
       </c>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>7</v>
       </c>
@@ -6862,7 +6883,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [Transportador autônomo de carga],</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>7</v>
       </c>
@@ -6883,7 +6904,7 @@
 – Transportador autônomo de passageiros],</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>7</v>
       </c>
@@ -6906,7 +6927,7 @@
 intermédio de Cooperativa de Trabalho],</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
         <v>7</v>
       </c>
@@ -6929,7 +6950,7 @@
 serviços por intermédio de cooperativa de trabalho],</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>7</v>
       </c>
@@ -6948,7 +6969,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [206 - Médico Residente, categoria e-Social 902 - Médico Residente],</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>7</v>
       </c>
@@ -6967,7 +6988,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [207 - MEI - Microempreendedor Individual, categoria e-Social 741 -Contribuinte individual - Microempreendedor Individual],</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
         <v>7</v>
       </c>
@@ -6986,7 +7007,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [301 - Empregado(a) Doméstico(a), categoria e-Social 104 - Empregado-Doméstico],</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
         <v>7</v>
       </c>
@@ -7009,7 +7030,7 @@
 contratado pela CLT],</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
         <v>7</v>
       </c>
@@ -7030,7 +7051,7 @@
 uma das demais categorias de contribuinte individual],</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>7</v>
       </c>
@@ -7051,7 +7072,7 @@
 711 - Contribuinte individual – Transportador autônomo de passageiros],</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>7</v>
       </c>
@@ -7072,7 +7093,7 @@
 - Contribuinte individual – Transportador autônomo de carga],</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
         <v>7</v>
       </c>
@@ -7095,7 +7116,7 @@
 ou indireta contratado pela CLT],</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>1</v>
       </c>
@@ -7117,7 +7138,7 @@
         <v>'' AS [Tipo de Admissão para o eSocial],</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
         <v>7</v>
       </c>
@@ -7128,7 +7149,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
         <v>7</v>
       </c>
@@ -7139,7 +7160,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
         <v>7</v>
       </c>
@@ -7150,7 +7171,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>7</v>
       </c>
@@ -7177,16 +7198,16 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7218,7 +7239,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -7252,7 +7273,7 @@
         <v>LEFT(CAST(PFUNCAO.CODIGO AS VARCHAR), 8) AS [Código do Cargo],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -7286,7 +7307,7 @@
         <v>LEFT(CAST(PFUNCAO.NOME AS VARCHAR), 40) AS [Descrição do Cargo],</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7331,20 +7352,20 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8CF3DA-54E2-4741-86F9-6B470B8650C3}">
   <dimension ref="A1:G321"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="9.109375" style="3"/>
+    <col min="1" max="1" width="26.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>11</v>
       </c>
@@ -7352,7 +7373,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>21</v>
       </c>
@@ -7360,7 +7381,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>22</v>
       </c>
@@ -7368,7 +7389,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>31</v>
       </c>
@@ -7376,7 +7397,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>32</v>
       </c>
@@ -7384,7 +7405,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>33</v>
       </c>
@@ -7392,7 +7413,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>41</v>
       </c>
@@ -7400,7 +7421,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>51</v>
       </c>
@@ -7408,7 +7429,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>52</v>
       </c>
@@ -7416,7 +7437,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>61</v>
       </c>
@@ -7424,7 +7445,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>71</v>
       </c>
@@ -7432,7 +7453,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>81</v>
       </c>
@@ -7440,7 +7461,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>91</v>
       </c>
@@ -7448,7 +7469,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>92</v>
       </c>
@@ -7456,15 +7477,15 @@
         <v>398</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>0</v>
       </c>
@@ -7472,7 +7493,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>1</v>
       </c>
@@ -7480,7 +7501,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>2</v>
       </c>
@@ -7488,7 +7509,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>3</v>
       </c>
@@ -7496,12 +7517,12 @@
         <v>403</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>1</v>
       </c>
@@ -7509,7 +7530,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>2</v>
       </c>
@@ -7517,7 +7538,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>3</v>
       </c>
@@ -7525,7 +7546,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>4</v>
       </c>
@@ -7533,12 +7554,12 @@
         <v>408</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>1</v>
       </c>
@@ -7546,7 +7567,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>2</v>
       </c>
@@ -7554,7 +7575,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>3</v>
       </c>
@@ -7562,7 +7583,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>4</v>
       </c>
@@ -7570,7 +7591,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>5</v>
       </c>
@@ -7578,7 +7599,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>6</v>
       </c>
@@ -7586,7 +7607,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>7</v>
       </c>
@@ -7594,12 +7615,12 @@
         <v>416</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>418</v>
       </c>
@@ -7607,7 +7628,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>420</v>
       </c>
@@ -7615,7 +7636,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>422</v>
       </c>
@@ -7623,7 +7644,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>424</v>
       </c>
@@ -7631,7 +7652,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>426</v>
       </c>
@@ -7639,7 +7660,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>428</v>
       </c>
@@ -7647,7 +7668,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>430</v>
       </c>
@@ -7655,7 +7676,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>432</v>
       </c>
@@ -7663,7 +7684,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>434</v>
       </c>
@@ -7671,7 +7692,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
         <v>436</v>
       </c>
@@ -7682,7 +7703,7 @@
       <c r="F50" s="10"/>
       <c r="G50" s="11"/>
     </row>
-    <row r="51" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>437</v>
       </c>
@@ -7695,7 +7716,7 @@
       <c r="F51" s="10"/>
       <c r="G51" s="11"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>439</v>
       </c>
@@ -7708,7 +7729,7 @@
       <c r="F52" s="10"/>
       <c r="G52" s="11"/>
     </row>
-    <row r="53" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>441</v>
       </c>
@@ -7721,7 +7742,7 @@
       <c r="F53" s="10"/>
       <c r="G53" s="11"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>443</v>
       </c>
@@ -7734,7 +7755,7 @@
       <c r="F54" s="10"/>
       <c r="G54" s="11"/>
     </row>
-    <row r="55" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>12</v>
       </c>
@@ -7747,7 +7768,7 @@
       <c r="F55" s="10"/>
       <c r="G55" s="11"/>
     </row>
-    <row r="56" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>446</v>
       </c>
@@ -7760,7 +7781,7 @@
       <c r="F56" s="10"/>
       <c r="G56" s="11"/>
     </row>
-    <row r="57" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>5</v>
       </c>
@@ -7773,7 +7794,7 @@
       <c r="F57" s="10"/>
       <c r="G57" s="11"/>
     </row>
-    <row r="58" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>449</v>
       </c>
@@ -7786,7 +7807,7 @@
       <c r="F58" s="10"/>
       <c r="G58" s="11"/>
     </row>
-    <row r="59" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>451</v>
       </c>
@@ -7799,7 +7820,7 @@
       <c r="F59" s="10"/>
       <c r="G59" s="11"/>
     </row>
-    <row r="60" spans="1:7" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="54" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>453</v>
       </c>
@@ -7812,7 +7833,7 @@
       <c r="F60" s="10"/>
       <c r="G60" s="11"/>
     </row>
-    <row r="61" spans="1:7" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="54" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>455</v>
       </c>
@@ -7825,7 +7846,7 @@
       <c r="F61" s="10"/>
       <c r="G61" s="11"/>
     </row>
-    <row r="62" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>457</v>
       </c>
@@ -7838,7 +7859,7 @@
       <c r="F62" s="10"/>
       <c r="G62" s="11"/>
     </row>
-    <row r="63" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>459</v>
       </c>
@@ -7851,7 +7872,7 @@
       <c r="F63" s="10"/>
       <c r="G63" s="11"/>
     </row>
-    <row r="64" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>461</v>
       </c>
@@ -7864,7 +7885,7 @@
       <c r="F64" s="10"/>
       <c r="G64" s="11"/>
     </row>
-    <row r="65" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>463</v>
       </c>
@@ -7877,7 +7898,7 @@
       <c r="F65" s="10"/>
       <c r="G65" s="11"/>
     </row>
-    <row r="66" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>465</v>
       </c>
@@ -7890,7 +7911,7 @@
       <c r="F66" s="10"/>
       <c r="G66" s="11"/>
     </row>
-    <row r="67" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A67" s="12" t="s">
         <v>467</v>
       </c>
@@ -7903,7 +7924,7 @@
       <c r="F67" s="10"/>
       <c r="G67" s="11"/>
     </row>
-    <row r="68" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A68" s="12" t="s">
         <v>469</v>
       </c>
@@ -7916,7 +7937,7 @@
       <c r="F68" s="10"/>
       <c r="G68" s="11"/>
     </row>
-    <row r="69" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
         <v>471</v>
       </c>
@@ -7929,7 +7950,7 @@
       <c r="F69" s="10"/>
       <c r="G69" s="11"/>
     </row>
-    <row r="70" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
         <v>473</v>
       </c>
@@ -7942,7 +7963,7 @@
       <c r="F70" s="10"/>
       <c r="G70" s="11"/>
     </row>
-    <row r="71" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A71" s="12" t="s">
         <v>475</v>
       </c>
@@ -7955,7 +7976,7 @@
       <c r="F71" s="10"/>
       <c r="G71" s="11"/>
     </row>
-    <row r="72" spans="1:7" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="54" x14ac:dyDescent="0.2">
       <c r="A72" s="12" t="s">
         <v>477</v>
       </c>
@@ -7968,7 +7989,7 @@
       <c r="F72" s="10"/>
       <c r="G72" s="11"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
         <v>479</v>
       </c>
@@ -7981,7 +8002,7 @@
       <c r="F73" s="10"/>
       <c r="G73" s="11"/>
     </row>
-    <row r="74" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>481</v>
       </c>
@@ -7994,7 +8015,7 @@
       <c r="F74" s="10"/>
       <c r="G74" s="11"/>
     </row>
-    <row r="75" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A75" s="12" t="s">
         <v>483</v>
       </c>
@@ -8007,7 +8028,7 @@
       <c r="F75" s="10"/>
       <c r="G75" s="11"/>
     </row>
-    <row r="76" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A76" s="12" t="s">
         <v>485</v>
       </c>
@@ -8020,7 +8041,7 @@
       <c r="F76" s="10"/>
       <c r="G76" s="11"/>
     </row>
-    <row r="77" spans="1:7" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="54" x14ac:dyDescent="0.2">
       <c r="A77" s="12" t="s">
         <v>487</v>
       </c>
@@ -8033,7 +8054,7 @@
       <c r="F77" s="10"/>
       <c r="G77" s="11"/>
     </row>
-    <row r="78" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A78" s="12" t="s">
         <v>489</v>
       </c>
@@ -8046,7 +8067,7 @@
       <c r="F78" s="10"/>
       <c r="G78" s="11"/>
     </row>
-    <row r="79" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A79" s="12" t="s">
         <v>491</v>
       </c>
@@ -8059,7 +8080,7 @@
       <c r="F79" s="10"/>
       <c r="G79" s="11"/>
     </row>
-    <row r="80" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A80" s="12" t="s">
         <v>493</v>
       </c>
@@ -8072,17 +8093,17 @@
       <c r="F80" s="10"/>
       <c r="G80" s="11"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="C81" s="4"/>
       <c r="E81" s="4"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="14" t="s">
         <v>496</v>
       </c>
@@ -8090,7 +8111,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="14" t="s">
         <v>1</v>
       </c>
@@ -8098,12 +8119,12 @@
         <v>498</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>0</v>
       </c>
@@ -8111,7 +8132,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>1</v>
       </c>
@@ -8119,7 +8140,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>2</v>
       </c>
@@ -8127,7 +8148,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>3</v>
       </c>
@@ -8135,7 +8156,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>4</v>
       </c>
@@ -8143,7 +8164,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>5</v>
       </c>
@@ -8151,7 +8172,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>6</v>
       </c>
@@ -8159,7 +8180,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>7</v>
       </c>
@@ -8167,7 +8188,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>9</v>
       </c>
@@ -8175,7 +8196,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>509</v>
       </c>
@@ -8183,7 +8204,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>511</v>
       </c>
@@ -8191,7 +8212,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>6</v>
       </c>
@@ -8199,7 +8220,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>2</v>
       </c>
@@ -8207,12 +8228,12 @@
         <v>514</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>0</v>
       </c>
@@ -8220,7 +8241,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>1</v>
       </c>
@@ -8228,7 +8249,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>2</v>
       </c>
@@ -8236,7 +8257,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>3</v>
       </c>
@@ -8244,7 +8265,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>4</v>
       </c>
@@ -8252,7 +8273,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>5</v>
       </c>
@@ -8260,7 +8281,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>6</v>
       </c>
@@ -8268,12 +8289,12 @@
         <v>522</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" s="14" t="s">
         <v>524</v>
       </c>
@@ -8281,7 +8302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" s="14" t="s">
         <v>17</v>
       </c>
@@ -8289,12 +8310,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>1</v>
       </c>
@@ -8302,7 +8323,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>2</v>
       </c>
@@ -8310,7 +8331,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>3</v>
       </c>
@@ -8318,7 +8339,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>4</v>
       </c>
@@ -8326,7 +8347,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>5</v>
       </c>
@@ -8334,12 +8355,12 @@
         <v>530</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>1</v>
       </c>
@@ -8347,7 +8368,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>2</v>
       </c>
@@ -8355,7 +8376,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>3</v>
       </c>
@@ -8363,7 +8384,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>4</v>
       </c>
@@ -8371,7 +8392,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>5</v>
       </c>
@@ -8379,7 +8400,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>6</v>
       </c>
@@ -8387,7 +8408,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>7</v>
       </c>
@@ -8395,7 +8416,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>9</v>
       </c>
@@ -8403,7 +8424,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>10</v>
       </c>
@@ -8411,7 +8432,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>11</v>
       </c>
@@ -8419,7 +8440,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>12</v>
       </c>
@@ -8427,7 +8448,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>13</v>
       </c>
@@ -8435,12 +8456,12 @@
         <v>542</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>1</v>
       </c>
@@ -8448,7 +8469,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>2</v>
       </c>
@@ -8456,7 +8477,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>4</v>
       </c>
@@ -8464,7 +8485,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>6</v>
       </c>
@@ -8472,7 +8493,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>8</v>
       </c>
@@ -8480,7 +8501,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>9</v>
       </c>
@@ -8488,12 +8509,12 @@
         <v>549</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>0</v>
       </c>
@@ -8501,7 +8522,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>1</v>
       </c>
@@ -8509,7 +8530,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>2</v>
       </c>
@@ -8517,7 +8538,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>3</v>
       </c>
@@ -8525,7 +8546,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>4</v>
       </c>
@@ -8533,7 +8554,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>5</v>
       </c>
@@ -8541,12 +8562,12 @@
         <v>556</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>0</v>
       </c>
@@ -8554,7 +8575,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>1</v>
       </c>
@@ -8562,12 +8583,12 @@
         <v>559</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" s="14" t="s">
         <v>560</v>
       </c>
@@ -8575,7 +8596,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="14" t="s">
         <v>562</v>
       </c>
@@ -8583,7 +8604,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" s="14" t="s">
         <v>564</v>
       </c>
@@ -8591,7 +8612,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" s="14" t="s">
         <v>566</v>
       </c>
@@ -8599,7 +8620,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" s="14" t="s">
         <v>568</v>
       </c>
@@ -8607,7 +8628,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" s="14" t="s">
         <v>570</v>
       </c>
@@ -8615,7 +8636,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="14" t="s">
         <v>572</v>
       </c>
@@ -8623,7 +8644,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" s="14" t="s">
         <v>574</v>
       </c>
@@ -8631,7 +8652,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" s="14" t="s">
         <v>576</v>
       </c>
@@ -8639,7 +8660,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" s="14" t="s">
         <v>578</v>
       </c>
@@ -8647,7 +8668,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" s="14" t="s">
         <v>580</v>
       </c>
@@ -8655,7 +8676,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" s="14" t="s">
         <v>582</v>
       </c>
@@ -8663,7 +8684,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" s="14" t="s">
         <v>584</v>
       </c>
@@ -8671,7 +8692,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" s="14" t="s">
         <v>586</v>
       </c>
@@ -8679,7 +8700,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" s="14" t="s">
         <v>588</v>
       </c>
@@ -8687,7 +8708,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" s="14" t="s">
         <v>590</v>
       </c>
@@ -8695,7 +8716,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" s="14" t="s">
         <v>592</v>
       </c>
@@ -8703,7 +8724,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" s="14" t="s">
         <v>594</v>
       </c>
@@ -8711,7 +8732,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" s="14" t="s">
         <v>596</v>
       </c>
@@ -8719,7 +8740,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" s="14" t="s">
         <v>598</v>
       </c>
@@ -8727,7 +8748,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="14" t="s">
         <v>600</v>
       </c>
@@ -8735,7 +8756,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" s="14" t="s">
         <v>602</v>
       </c>
@@ -8743,7 +8764,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" s="14" t="s">
         <v>604</v>
       </c>
@@ -8751,7 +8772,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" s="14" t="s">
         <v>606</v>
       </c>
@@ -8759,7 +8780,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" s="14" t="s">
         <v>608</v>
       </c>
@@ -8767,7 +8788,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" s="14" t="s">
         <v>610</v>
       </c>
@@ -8775,7 +8796,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" s="14" t="s">
         <v>612</v>
       </c>
@@ -8783,12 +8804,12 @@
         <v>613</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" s="16" t="s">
         <v>420</v>
       </c>
@@ -8796,7 +8817,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" s="16" t="s">
         <v>422</v>
       </c>
@@ -8804,7 +8825,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" s="16" t="s">
         <v>424</v>
       </c>
@@ -8812,7 +8833,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" s="16" t="s">
         <v>426</v>
       </c>
@@ -8820,7 +8841,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" s="16" t="s">
         <v>428</v>
       </c>
@@ -8828,7 +8849,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" s="16" t="s">
         <v>430</v>
       </c>
@@ -8836,7 +8857,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" s="16" t="s">
         <v>432</v>
       </c>
@@ -8844,7 +8865,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" s="16" t="s">
         <v>434</v>
       </c>
@@ -8852,7 +8873,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" s="16">
         <v>90</v>
       </c>
@@ -8860,7 +8881,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A194" s="16">
         <v>97</v>
       </c>
@@ -8868,7 +8889,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" s="16">
         <v>98</v>
       </c>
@@ -8876,7 +8897,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" s="16">
         <v>99</v>
       </c>
@@ -8884,12 +8905,12 @@
         <v>626</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" s="14">
         <v>10</v>
       </c>
@@ -8897,7 +8918,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" s="14">
         <v>20</v>
       </c>
@@ -8905,7 +8926,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" s="14">
         <v>21</v>
       </c>
@@ -8913,7 +8934,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" s="14">
         <v>22</v>
       </c>
@@ -8921,7 +8942,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" s="14">
         <v>23</v>
       </c>
@@ -8929,7 +8950,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" s="14">
         <v>24</v>
       </c>
@@ -8937,7 +8958,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" s="14">
         <v>25</v>
       </c>
@@ -8945,7 +8966,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" s="14">
         <v>26</v>
       </c>
@@ -8953,7 +8974,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" s="14">
         <v>27</v>
       </c>
@@ -8961,7 +8982,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" s="14">
         <v>28</v>
       </c>
@@ -8969,7 +8990,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" s="14">
         <v>29</v>
       </c>
@@ -8977,7 +8998,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" s="14">
         <v>30</v>
       </c>
@@ -8985,7 +9006,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" s="14">
         <v>31</v>
       </c>
@@ -8993,7 +9014,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" s="14">
         <v>32</v>
       </c>
@@ -9001,7 +9022,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" s="14">
         <v>34</v>
       </c>
@@ -9009,7 +9030,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" s="14">
         <v>35</v>
       </c>
@@ -9017,7 +9038,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" s="14">
         <v>36</v>
       </c>
@@ -9025,7 +9046,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" s="14">
         <v>37</v>
       </c>
@@ -9033,7 +9054,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" s="14">
         <v>38</v>
       </c>
@@ -9041,7 +9062,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" s="14">
         <v>39</v>
       </c>
@@ -9049,7 +9070,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" s="14">
         <v>40</v>
       </c>
@@ -9057,7 +9078,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" s="14">
         <v>41</v>
       </c>
@@ -9065,7 +9086,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" s="14">
         <v>42</v>
       </c>
@@ -9073,7 +9094,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" s="14">
         <v>43</v>
       </c>
@@ -9081,7 +9102,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" s="14">
         <v>44</v>
       </c>
@@ -9089,7 +9110,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" s="14">
         <v>45</v>
       </c>
@@ -9097,7 +9118,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" s="14">
         <v>46</v>
       </c>
@@ -9105,7 +9126,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" s="14">
         <v>47</v>
       </c>
@@ -9113,7 +9134,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" s="14">
         <v>48</v>
       </c>
@@ -9121,7 +9142,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" s="14">
         <v>49</v>
       </c>
@@ -9129,7 +9150,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" s="14">
         <v>50</v>
       </c>
@@ -9137,7 +9158,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" s="14">
         <v>51</v>
       </c>
@@ -9145,7 +9166,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" s="14">
         <v>60</v>
       </c>
@@ -9153,7 +9174,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" s="14">
         <v>61</v>
       </c>
@@ -9161,7 +9182,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" s="14">
         <v>62</v>
       </c>
@@ -9169,7 +9190,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" s="14">
         <v>70</v>
       </c>
@@ -9177,12 +9198,12 @@
         <v>662</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
         <v>1</v>
       </c>
@@ -9190,7 +9211,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
         <v>2</v>
       </c>
@@ -9198,12 +9219,12 @@
         <v>665</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="241" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
         <v>437</v>
       </c>
@@ -9211,7 +9232,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="242" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A242" s="17" t="s">
         <v>439</v>
       </c>
@@ -9219,7 +9240,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="243" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
         <v>441</v>
       </c>
@@ -9227,7 +9248,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="244" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A244" s="17" t="s">
         <v>670</v>
       </c>
@@ -9235,7 +9256,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="245" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A245" s="17" t="s">
         <v>12</v>
       </c>
@@ -9243,7 +9264,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="246" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A246" s="17" t="s">
         <v>446</v>
       </c>
@@ -9251,7 +9272,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="247" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A247" s="17" t="s">
         <v>5</v>
       </c>
@@ -9259,7 +9280,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="248" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A248" s="17" t="s">
         <v>449</v>
       </c>
@@ -9267,7 +9288,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="249" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A249" s="17" t="s">
         <v>451</v>
       </c>
@@ -9275,7 +9296,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="250" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A250" s="17" t="s">
         <v>677</v>
       </c>
@@ -9283,7 +9304,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="251" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A251" s="17" t="s">
         <v>453</v>
       </c>
@@ -9291,7 +9312,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="252" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A252" s="17" t="s">
         <v>455</v>
       </c>
@@ -9299,7 +9320,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="253" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A253" s="17" t="s">
         <v>457</v>
       </c>
@@ -9307,7 +9328,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="254" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A254" s="17" t="s">
         <v>459</v>
       </c>
@@ -9315,7 +9336,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="255" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A255" s="17" t="s">
         <v>683</v>
       </c>
@@ -9323,7 +9344,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="256" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A256" s="17" t="s">
         <v>685</v>
       </c>
@@ -9331,7 +9352,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="257" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A257" s="17" t="s">
         <v>687</v>
       </c>
@@ -9339,7 +9360,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="258" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A258" s="17" t="s">
         <v>689</v>
       </c>
@@ -9347,7 +9368,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="259" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A259" s="17" t="s">
         <v>691</v>
       </c>
@@ -9355,7 +9376,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="260" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A260" s="17" t="s">
         <v>693</v>
       </c>
@@ -9363,7 +9384,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="261" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A261" s="17" t="s">
         <v>695</v>
       </c>
@@ -9371,7 +9392,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="262" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A262" s="17" t="s">
         <v>697</v>
       </c>
@@ -9379,7 +9400,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="263" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A263" s="17" t="s">
         <v>699</v>
       </c>
@@ -9387,7 +9408,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="264" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A264" s="17" t="s">
         <v>701</v>
       </c>
@@ -9395,7 +9416,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="265" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A265" s="17" t="s">
         <v>703</v>
       </c>
@@ -9403,7 +9424,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="266" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A266" s="17" t="s">
         <v>705</v>
       </c>
@@ -9411,7 +9432,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="267" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A267" s="17" t="s">
         <v>707</v>
       </c>
@@ -9419,7 +9440,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="268" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A268" s="17" t="s">
         <v>709</v>
       </c>
@@ -9427,7 +9448,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="269" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A269" s="17" t="s">
         <v>10</v>
       </c>
@@ -9435,7 +9456,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="270" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A270" s="17" t="s">
         <v>712</v>
       </c>
@@ -9443,7 +9464,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="271" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A271" s="17" t="s">
         <v>714</v>
       </c>
@@ -9451,7 +9472,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="272" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A272" s="17" t="s">
         <v>716</v>
       </c>
@@ -9459,7 +9480,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A273" s="17" t="s">
         <v>718</v>
       </c>
@@ -9467,7 +9488,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A274" s="17" t="s">
         <v>720</v>
       </c>
@@ -9475,7 +9496,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A275" s="17" t="s">
         <v>722</v>
       </c>
@@ -9483,7 +9504,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A276" s="17" t="s">
         <v>724</v>
       </c>
@@ -9491,7 +9512,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A277" s="17" t="s">
         <v>726</v>
       </c>
@@ -9499,7 +9520,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A278" s="17" t="s">
         <v>728</v>
       </c>
@@ -9507,7 +9528,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A279" s="17" t="s">
         <v>730</v>
       </c>
@@ -9515,7 +9536,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A280" s="17" t="s">
         <v>732</v>
       </c>
@@ -9523,7 +9544,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A281" s="17" t="s">
         <v>734</v>
       </c>
@@ -9531,7 +9552,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A282" s="17" t="s">
         <v>736</v>
       </c>
@@ -9539,7 +9560,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A283" s="17" t="s">
         <v>738</v>
       </c>
@@ -9547,7 +9568,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A284" s="17" t="s">
         <v>740</v>
       </c>
@@ -9555,7 +9576,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A285" s="17" t="s">
         <v>742</v>
       </c>
@@ -9563,12 +9584,12 @@
         <v>743</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A288" s="18" t="s">
         <v>443</v>
       </c>
@@ -9579,7 +9600,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A289" s="18" t="s">
         <v>449</v>
       </c>
@@ -9590,7 +9611,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A290" s="18" t="s">
         <v>451</v>
       </c>
@@ -9601,7 +9622,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A291" s="18" t="s">
         <v>677</v>
       </c>
@@ -9612,7 +9633,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A292" s="18" t="s">
         <v>453</v>
       </c>
@@ -9623,7 +9644,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A293" s="18" t="s">
         <v>455</v>
       </c>
@@ -9634,7 +9655,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A294" s="18" t="s">
         <v>457</v>
       </c>
@@ -9645,7 +9666,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A295" s="18" t="s">
         <v>685</v>
       </c>
@@ -9656,7 +9677,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A296" s="18" t="s">
         <v>689</v>
       </c>
@@ -9667,7 +9688,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A297" s="18" t="s">
         <v>691</v>
       </c>
@@ -9678,7 +9699,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A298" s="18" t="s">
         <v>693</v>
       </c>
@@ -9689,7 +9710,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A299" s="18" t="s">
         <v>695</v>
       </c>
@@ -9700,7 +9721,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A300" s="18" t="s">
         <v>697</v>
       </c>
@@ -9711,7 +9732,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A301" s="18" t="s">
         <v>699</v>
       </c>
@@ -9722,7 +9743,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A302" s="18" t="s">
         <v>757</v>
       </c>
@@ -9733,7 +9754,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A303" s="18" t="s">
         <v>705</v>
       </c>
@@ -9744,7 +9765,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A304" s="18" t="s">
         <v>707</v>
       </c>
@@ -9755,7 +9776,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A305" s="18" t="s">
         <v>709</v>
       </c>
@@ -9766,7 +9787,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A306" s="18" t="s">
         <v>720</v>
       </c>
@@ -9777,7 +9798,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A307" s="18" t="s">
         <v>722</v>
       </c>
@@ -9788,7 +9809,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A308" s="18" t="s">
         <v>10</v>
       </c>
@@ -9799,7 +9820,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A309" s="18" t="s">
         <v>712</v>
       </c>
@@ -9810,7 +9831,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A310" s="18" t="s">
         <v>763</v>
       </c>
@@ -9821,7 +9842,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A311" s="18" t="s">
         <v>714</v>
       </c>
@@ -9832,7 +9853,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A312" s="18" t="s">
         <v>716</v>
       </c>
@@ -9843,7 +9864,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A313" s="18" t="s">
         <v>718</v>
       </c>
@@ -9854,7 +9875,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A314" s="18" t="s">
         <v>766</v>
       </c>
@@ -9865,7 +9886,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A315" s="18" t="s">
         <v>768</v>
       </c>
@@ -9876,7 +9897,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A316" s="18" t="s">
         <v>769</v>
       </c>
@@ -9887,7 +9908,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" ht="21.75" x14ac:dyDescent="0.2">
       <c r="A319" s="19" t="s">
         <v>771</v>
       </c>
@@ -9896,7 +9917,7 @@
       </c>
       <c r="C319" s="15"/>
     </row>
-    <row r="320" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A320" s="18" t="s">
         <v>773</v>
       </c>
@@ -9905,7 +9926,7 @@
       </c>
       <c r="C320" s="15"/>
     </row>
-    <row r="321" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A321" s="18" t="s">
         <v>775</v>
       </c>
@@ -9931,16 +9952,16 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9972,7 +9993,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -10003,7 +10024,7 @@
         <v>LEFT(CAST(PFFINANC.CODCOLIGADA AS VARCHAR), 4) AS [Código da Unidade, cfe. Tabela de Unidades],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -10034,7 +10055,7 @@
         <v>LEFT(CAST(PFUNC.CHAPA AS VARCHAR), 8) AS [Código do Contrato],</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8</v>
       </c>
@@ -10052,11 +10073,11 @@
         <v>[Data Base da Folha de Pagamento. Sugerimos o último dia de cada mês para as Folhas Mensais.]</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" ref="J3:J30" si="1">"'' AS "&amp;F4&amp;","</f>
+        <f t="shared" ref="J4:J30" si="1">"'' AS "&amp;F4&amp;","</f>
         <v>'' AS [Data Base da Folha de Pagamento. Sugerimos o último dia de cada mês para as Folhas Mensais.],</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -10078,7 +10099,7 @@
         <v>'' AS [Código da Folha de Pagamento],</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -10097,7 +10118,7 @@
         <v>'' AS [11 – Mensal],</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>7</v>
       </c>
@@ -10116,7 +10137,7 @@
         <v>'' AS [21 – Quinzenal – 1ª Quinzena],</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -10135,7 +10156,7 @@
         <v>'' AS [22 – Quinzenal – 2ª Quinzena],</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -10154,7 +10175,7 @@
         <v>'' AS [31 – Semanal – 1ª Semana],</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>7</v>
       </c>
@@ -10173,7 +10194,7 @@
         <v>'' AS [32 – Semanal – Semanas Intermediárias],</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -10192,7 +10213,7 @@
         <v>'' AS [33 – Semanal – Última Semana],</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>7</v>
       </c>
@@ -10211,7 +10232,7 @@
         <v>'' AS [41 – Adiantamento Quinzenal],</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>7</v>
       </c>
@@ -10230,7 +10251,7 @@
         <v>'' AS [51 – 13° Salário – Antecipação],</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>7</v>
       </c>
@@ -10249,7 +10270,7 @@
         <v>'' AS [52 – 13° Salário - Complementação],</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>7</v>
       </c>
@@ -10268,7 +10289,7 @@
         <v>'' AS [61 – Suplementar],</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>7</v>
       </c>
@@ -10287,7 +10308,7 @@
         <v>'' AS [71 – Avulsa],</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>7</v>
       </c>
@@ -10306,7 +10327,7 @@
         <v>'' AS [81 – Recibos de Férias],</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>7</v>
       </c>
@@ -10325,7 +10346,7 @@
         <v>'' AS [91 – Rescisão de Contrato],</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>7</v>
       </c>
@@ -10344,7 +10365,7 @@
         <v>'' AS [92 – Rescisão Complementar],</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>5</v>
       </c>
@@ -10366,7 +10387,7 @@
         <v>'' AS [Código do VDB],</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>8</v>
       </c>
@@ -10388,7 +10409,7 @@
         <v>'' AS [Data de Pagamento da Folha de Pagamento],</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
@@ -10410,7 +10431,7 @@
         <v>'' AS [Tipo de Informação],</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>7</v>
       </c>
@@ -10429,7 +10450,7 @@
         <v>'' AS [0 – Só Valor],</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>7</v>
       </c>
@@ -10448,7 +10469,7 @@
         <v>'' AS [1 – Horas e Valor],</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>7</v>
       </c>
@@ -10467,7 +10488,7 @@
         <v>'' AS [2 – Dias e Valor],</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>7</v>
       </c>
@@ -10486,7 +10507,7 @@
         <v>'' AS [3 – Quantidade de Tarefas e Valor],</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>11</v>
       </c>
@@ -10511,7 +10532,7 @@
         <v>'' AS [Horas, Dias ou Quantidade, cfe. Tipo de Informação. Zeros quando o Tipo de Informação for “0”.],</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>15</v>
       </c>
@@ -10545,7 +10566,7 @@
         <v>LEFT(CAST(PFFINANC.VALOR AS DECIMAL), 15) AS [Valor],</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>30</v>
       </c>
@@ -10567,7 +10588,7 @@
         <v>'' AS [Identificador atribuído pela fonte pagadora para o demonstrativo de valores devidos ao trabalhador, gerado no eSocial.],</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>100</v>
       </c>
@@ -10604,16 +10625,16 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10645,7 +10666,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>5</v>
       </c>
@@ -10670,7 +10691,7 @@
         <v>'' AS [Código do Vencimento, Desconto ou Base Metadados (Destino)],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7</v>
       </c>
@@ -10704,7 +10725,7 @@
         <v>LEFT(CAST(PEVENTO.CODIGO AS VARCHAR), 7) AS [Código do Vencimento, Desconto ou Base do sistema de Origem],</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>30</v>
       </c>
@@ -10738,7 +10759,7 @@
         <v>LEFT(CAST(PEVENTO.DESCRICAO AS VARCHAR), 30) AS [Descrição do VDB],</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -10763,7 +10784,7 @@
         <v>'' AS [Tipo do VDB],</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -10781,7 +10802,7 @@
         <v>[V – Vencimento]</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>7</v>
       </c>
@@ -10799,7 +10820,7 @@
         <v>[D – Desconto]</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -10832,16 +10853,16 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="65.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10873,7 +10894,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -10907,7 +10928,7 @@
         <v>LEFT(CAST(PFHSTAFT.CODCOLIGADA AS VARCHAR), 4) AS [Código da Unidade, cfe. Tabela de Unidades],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -10932,7 +10953,7 @@
         <v>'' AS [Código do Contrato],</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8</v>
       </c>
@@ -10966,7 +10987,7 @@
         <v>FORMAT(PFHSTAFT.DTMUDANCA, 'ddMMyyyy') AS [Data de Início da Ocorrência],</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -11000,7 +11021,7 @@
         <v>LEFT(CAST(PFHSTAFT.MOTIVO AS VARCHAR), 4) AS [Ocorrência],</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -11014,11 +11035,11 @@
         <v>204</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" ref="J5:J36" si="1">"'' AS "&amp;F6&amp;","</f>
+        <f t="shared" ref="J6:J35" si="1">"'' AS "&amp;F6&amp;","</f>
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>7</v>
       </c>
@@ -11036,7 +11057,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -11054,7 +11075,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -11072,7 +11093,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>7</v>
       </c>
@@ -11090,7 +11111,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -11108,7 +11129,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>7</v>
       </c>
@@ -11126,7 +11147,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>7</v>
       </c>
@@ -11144,7 +11165,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>7</v>
       </c>
@@ -11162,7 +11183,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>7</v>
       </c>
@@ -11180,7 +11201,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>7</v>
       </c>
@@ -11198,7 +11219,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="17" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>7</v>
       </c>
@@ -11216,7 +11237,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="18" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>7</v>
       </c>
@@ -11234,7 +11255,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="19" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>7</v>
       </c>
@@ -11252,7 +11273,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="20" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>7</v>
       </c>
@@ -11270,7 +11291,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="21" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>7</v>
       </c>
@@ -11288,7 +11309,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="22" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>7</v>
       </c>
@@ -11306,7 +11327,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="23" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>7</v>
       </c>
@@ -11324,7 +11345,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="24" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>7</v>
       </c>
@@ -11342,7 +11363,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="25" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>7</v>
       </c>
@@ -11360,7 +11381,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="26" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>7</v>
       </c>
@@ -11378,7 +11399,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="27" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>7</v>
       </c>
@@ -11396,7 +11417,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="28" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>7</v>
       </c>
@@ -11414,7 +11435,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="29" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>7</v>
       </c>
@@ -11432,7 +11453,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="30" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>7</v>
       </c>
@@ -11450,7 +11471,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="31" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>7</v>
       </c>
@@ -11468,7 +11489,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="32" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>7</v>
       </c>
@@ -11486,7 +11507,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>7</v>
       </c>
@@ -11504,7 +11525,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>8</v>
       </c>
@@ -11529,7 +11550,7 @@
         <v>'' AS [Data de Término da Ocorrência],</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>6</v>
       </c>
@@ -11554,7 +11575,7 @@
         <v>'' AS [Horas da ocorrência quando for somente um dia (Formato: HHH:MM)],</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1000</v>
       </c>
@@ -11603,16 +11624,16 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J88"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11644,7 +11665,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -11669,7 +11690,7 @@
         <v>'' AS [Código da Empresa, cfe. Tabela de Empresas],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -11703,7 +11724,7 @@
         <v>LEFT(CAST(PPESSOA.CODIGO AS INTEGER), 8) AS [Código da Pessoa],</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>40</v>
       </c>
@@ -11737,7 +11758,7 @@
         <v>LEFT(CAST(PPESSOA.NOME AS VARCHAR), 40) AS [Nome da Pessoa],</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>40</v>
       </c>
@@ -11758,11 +11779,11 @@
         <v>[Nome do Pai]</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" ref="J3:J68" si="3">"'' AS "&amp;F5&amp;","</f>
+        <f t="shared" ref="J5:J68" si="3">"'' AS "&amp;F5&amp;","</f>
         <v>'' AS [Nome do Pai],</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>40</v>
       </c>
@@ -11787,7 +11808,7 @@
         <v>'' AS [Nome da Mãe],</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>8</v>
       </c>
@@ -11821,7 +11842,7 @@
         <v>LEFT(CAST(PPESSOA.DTNASCIMENTO AS DATE), 8) AS [Data de Nascimento],</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>20</v>
       </c>
@@ -11855,7 +11876,7 @@
         <v>LEFT(CAST(PPESSOA.MUNICIPIO AS VARCHAR), 20) AS [Local do Nascimento],</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
@@ -11889,7 +11910,7 @@
         <v>LEFT(CAST(PPESSOA.UF AS VARCHAR), 2) AS [UF do Nascimento],</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -11923,7 +11944,7 @@
         <v>LEFT(CAST(PPESSOA.SEXO AS VARCHAR), 1) AS [Sexo],</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -11945,7 +11966,7 @@
         <v>'' AS [M – Masculino],</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>7</v>
       </c>
@@ -11967,7 +11988,7 @@
         <v>'' AS [F – Feminino],</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
@@ -12001,7 +12022,7 @@
         <v>LEFT(CAST(PPESSOA.CORRACA AS VARCHAR), 1) AS [Raça/Cor],</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>7</v>
       </c>
@@ -12023,7 +12044,7 @@
         <v>'' AS [1 – Indígena],</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>7</v>
       </c>
@@ -12045,7 +12066,7 @@
         <v>'' AS [2 – Branca],</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>7</v>
       </c>
@@ -12067,7 +12088,7 @@
         <v>'' AS [4 – Preta],</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>7</v>
       </c>
@@ -12089,7 +12110,7 @@
         <v>'' AS [6 – Amarela],</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>7</v>
       </c>
@@ -12111,7 +12132,7 @@
         <v>'' AS [8 – Parda],</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>7</v>
       </c>
@@ -12133,7 +12154,7 @@
         <v>'' AS [9 - Não Informada],</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1</v>
       </c>
@@ -12158,7 +12179,7 @@
         <v>'' AS [Deficiente Físico],</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>7</v>
       </c>
@@ -12180,7 +12201,7 @@
         <v>'' AS [0 – Não Deficiente],</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>7</v>
       </c>
@@ -12202,7 +12223,7 @@
         <v>'' AS [1 – Deficiente Físico],</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>7</v>
       </c>
@@ -12224,7 +12245,7 @@
         <v>'' AS [2 – Deficiente Auditivo],</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>7</v>
       </c>
@@ -12246,7 +12267,7 @@
         <v>'' AS [3 – Deficiente Visual],</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>7</v>
       </c>
@@ -12268,7 +12289,7 @@
         <v>'' AS [4 – Deficiente Mental (Intelectual)],</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>7</v>
       </c>
@@ -12290,7 +12311,7 @@
         <v>'' AS [5 – Deficiente Múltiplo],</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>40</v>
       </c>
@@ -12324,7 +12345,7 @@
         <v>LEFT(CAST(PPESSOA.RUA AS VARCHAR), 40) AS [Rua (endereço)],</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>8</v>
       </c>
@@ -12358,7 +12379,7 @@
         <v>LEFT(CAST(PPESSOA.NUMERO AS VARCHAR), 8) AS [Número (endereço)],</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>20</v>
       </c>
@@ -12383,7 +12404,7 @@
         <v>'' AS [Complemento (endereço)],</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>20</v>
       </c>
@@ -12417,7 +12438,7 @@
         <v>LEFT(CAST(PPESSOA.BAIRRO AS VARCHAR), 20) AS [Bairro],</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>20</v>
       </c>
@@ -12451,7 +12472,7 @@
         <v>LEFT(CAST(PPESSOA.CIDADE AS VARCHAR), 20) AS [Cidade],</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>10</v>
       </c>
@@ -12485,7 +12506,7 @@
         <v>LEFT(CAST(PPESSOA.CEP AS VARCHAR), 10) AS [CEP],</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2</v>
       </c>
@@ -12519,7 +12540,7 @@
         <v>LEFT(CAST(PPESSOA.ESTADO AS VARCHAR), 2) AS [UF],</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>4</v>
       </c>
@@ -12544,7 +12565,7 @@
         <v>'' AS [DDD],</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>15</v>
       </c>
@@ -12578,7 +12599,7 @@
         <v>LEFT(CAST(PPESSOA.TELEFONE1 AS VARCHAR), 15) AS [Telefone],</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>40</v>
       </c>
@@ -12612,7 +12633,7 @@
         <v>LEFT(CAST(PPESSOA.EMAIL AS VARCHAR), 40) AS [Email],</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>11</v>
       </c>
@@ -12646,7 +12667,7 @@
         <v>LEFT(CAST(PFUNC.PISPASEP AS VARCHAR), 11) AS [PIS],</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>8</v>
       </c>
@@ -12671,7 +12692,7 @@
         <v>'' AS [Data do Cadastramento do PIS],</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>11</v>
       </c>
@@ -12705,7 +12726,7 @@
         <v>LEFT(CAST(PPESSOA.CPF AS VARCHAR), 11) AS [CPF],</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>15</v>
       </c>
@@ -12739,7 +12760,7 @@
         <v>LEFT(CAST(PPESSOA.CARTIDENTIDADE AS VARCHAR), 15) AS [Identidade (RE ou RG)],</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>8</v>
       </c>
@@ -12773,7 +12794,7 @@
         <v>FORMAT(PPESSOA.DTEMISSAOIDENT, 'ddMMyyyy') AS [Data da Emissão da Identidade],</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>8</v>
       </c>
@@ -12807,7 +12828,7 @@
         <v>LEFT(CAST(PPESSOA.ORGEMISSORIDENT AS VARCHAR), 8) AS [Órgão Emissor da Identidade],</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2</v>
       </c>
@@ -12841,7 +12862,7 @@
         <v>LEFT(CAST(PPESSOA.UFEMISSAOIDENT AS VARCHAR), 2) AS [UF da Identidade],</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>15</v>
       </c>
@@ -12875,7 +12896,7 @@
         <v>LEFT(CAST(PPESSOA.TITULOELEITOR AS VARCHAR), 15) AS [Título Eleitoral],</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>4</v>
       </c>
@@ -12909,7 +12930,7 @@
         <v>LEFT(CAST(PPESSOA.ZONATITELEITOR AS VARCHAR), 4) AS [Zona Eleitoral],</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>4</v>
       </c>
@@ -12943,7 +12964,7 @@
         <v>LEFT(CAST(PPESSOA.SECAOTITELEITOR AS VARCHAR), 4) AS [Seção Eleitoral],</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1</v>
       </c>
@@ -12968,7 +12989,7 @@
         <v>'' AS [Aposentado],</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>7</v>
       </c>
@@ -12990,7 +13011,7 @@
         <v>'' AS [0 – Não Aposentado],</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>7</v>
       </c>
@@ -13012,7 +13033,7 @@
         <v>'' AS [1 – Aposentado],</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>8</v>
       </c>
@@ -13037,7 +13058,7 @@
         <v>'' AS [Data da Aposentadoria],</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2</v>
       </c>
@@ -13071,7 +13092,7 @@
         <v>LEFT(CAST(PPESSOA.ESTADOCIVIL AS VARCHAR), 2) AS [Estado Civil],</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>7</v>
       </c>
@@ -13093,7 +13114,7 @@
         <v>'' AS [01 – Solteiro],</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>7</v>
       </c>
@@ -13115,7 +13136,7 @@
         <v>'' AS [02 – Casado],</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>7</v>
       </c>
@@ -13137,7 +13158,7 @@
         <v>'' AS [03 – Viúvo],</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>7</v>
       </c>
@@ -13159,7 +13180,7 @@
         <v>'' AS [04 – Separado],</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>7</v>
       </c>
@@ -13181,7 +13202,7 @@
         <v>'' AS [05 – Divorciado],</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2</v>
       </c>
@@ -13215,7 +13236,7 @@
         <v>LEFT(CAST(PPESSOA.GRAUINSTRUCAO AS VARCHAR), 2) AS [Grau de Instrução],</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>7</v>
       </c>
@@ -13237,7 +13258,7 @@
         <v>'' AS [01 – Analfabeto],</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>7</v>
       </c>
@@ -13259,7 +13280,7 @@
         <v>'' AS [02 – Até o 5º Ano Incompleto do Ensino Fundamental],</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>7</v>
       </c>
@@ -13281,7 +13302,7 @@
         <v>'' AS [03 – 5º Ano Completo do Ensino Fundamental],</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>7</v>
       </c>
@@ -13303,7 +13324,7 @@
         <v>'' AS [04 – Do 6º ao 9º Ano do Ensino Fundamental Incompleto],</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>7</v>
       </c>
@@ -13325,7 +13346,7 @@
         <v>'' AS [05 – Ensino Fundamental Completo],</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>7</v>
       </c>
@@ -13347,7 +13368,7 @@
         <v>'' AS [06 - Ensino Médio Incompleto],</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>7</v>
       </c>
@@ -13369,7 +13390,7 @@
         <v>'' AS [07 – Ensino Médio Completo],</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>7</v>
       </c>
@@ -13391,7 +13412,7 @@
         <v>'' AS [09 – Educação Superior Incompleta],</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>7</v>
       </c>
@@ -13413,7 +13434,7 @@
         <v>'' AS [10 – Educação Superior Completa],</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>7</v>
       </c>
@@ -13435,7 +13456,7 @@
         <v>'' AS [11 – Pós-Graduado],</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>7</v>
       </c>
@@ -13457,7 +13478,7 @@
         <v>'' AS [12 – Mestrado Completo],</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>7</v>
       </c>
@@ -13475,11 +13496,11 @@
         <v>[13 – Doutorado Completo]</v>
       </c>
       <c r="J69" t="str">
-        <f t="shared" ref="J69:J88" si="8">"'' AS "&amp;F69&amp;","</f>
+        <f t="shared" ref="J69:J82" si="8">"'' AS "&amp;F69&amp;","</f>
         <v>'' AS [13 – Doutorado Completo],</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2</v>
       </c>
@@ -13513,7 +13534,7 @@
         <v>LEFT(CAST(PPESSOA.NACIONALIDADE AS VARCHAR), 2) AS [Nacionalidade (cfe. Tabela da Rais)],</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>4</v>
       </c>
@@ -13538,7 +13559,7 @@
         <v>'' AS [DDD do Telefone Celular],</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>15</v>
       </c>
@@ -13563,7 +13584,7 @@
         <v>'' AS [Número do Telefone Celular],</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>20</v>
       </c>
@@ -13597,7 +13618,7 @@
         <v>LEFT(CAST(PPESSOA.CERTIFRESERV AS VARCHAR), 20) AS [Certificado de Reservista],</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>15</v>
       </c>
@@ -13631,7 +13652,7 @@
         <v>LEFT(CAST(PPESSOA.CARTMOTORISTA AS VARCHAR), 15) AS [Registro da Carteira de Habilitação],</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>3</v>
       </c>
@@ -13665,7 +13686,7 @@
         <v>LEFT(CAST(PPESSOA.TIPOCARTHABILIT AS VARCHAR), 3) AS [Categoria da Carteira de Habilitação],</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>8</v>
       </c>
@@ -13699,7 +13720,7 @@
         <v>FORMAT(PPESSOA.DATAVENCHABILIT, 'ddMMyyyy') AS [Data de Validade da Carteira de Habilitação],</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>20</v>
       </c>
@@ -13733,7 +13754,7 @@
         <v>LEFT(CAST(PPESSOA.ORGEMISSORCNH AS VARCHAR), 20) AS [Órgão Emissor da Carteira de Habilitação],</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2</v>
       </c>
@@ -13767,7 +13788,7 @@
         <v>LEFT(CAST(PPESSOA.UFCNH AS VARCHAR), 2) AS [UF da Carteira de Habilitação],</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>20</v>
       </c>
@@ -13801,7 +13822,7 @@
         <v>LEFT(CAST(PPESSOA.NUMEROCARTAOSUS AS VARCHAR), 20) AS [Número do Cartão do SUS],</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>14</v>
       </c>
@@ -13826,7 +13847,7 @@
         <v>'' AS [Número do Registro de Identidade Civil (RIC)],</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>8</v>
       </c>
@@ -13851,7 +13872,7 @@
         <v>'' AS [Data de Expedição do Registro de Identidade Civil (RIC)],</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>20</v>
       </c>
@@ -13876,7 +13897,7 @@
         <v>'' AS [Órgão Emissor do Registro de Identidade Civil (RIC)],</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>10</v>
       </c>
@@ -13910,7 +13931,7 @@
         <v>LEFT(CAST(PPESSOA.CARTEIRATRAB AS VARCHAR), 10) AS [Número da Carteira de Trabalho],</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>5</v>
       </c>
@@ -13944,7 +13965,7 @@
         <v>LEFT(CAST(PPESSOA.SERIECARTTRAB AS VARCHAR), 5) AS [Série da Carteira de Trabalho],</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>8</v>
       </c>
@@ -13978,7 +13999,7 @@
         <v>FORMAT(PPESSOA.DTCARTTRAB, 'ddMMyyyy') AS [Data de Emissão da Carteira de Trabalho],</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2</v>
       </c>
@@ -14012,7 +14033,7 @@
         <v>LEFT(CAST(PPESSOA.UFCARTTRAB AS VARCHAR), 2) AS [UF da Carteira de Trabalho],</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>70</v>
       </c>
@@ -14046,7 +14067,7 @@
         <v>LEFT(CAST(PPESSOA.NOME AS VARCHAR), 70) AS [Nome Completo],</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>8</v>
       </c>
@@ -14095,16 +14116,16 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14136,7 +14157,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -14170,7 +14191,7 @@
         <v>LEFT(CAST(PFUNC.CODFILIAL AS VARCHAR), 4) AS [Código da Unidade, cfe. Tabela de Unidades],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -14195,7 +14216,7 @@
         <v>'' AS [Código do Contrato],</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8</v>
       </c>
@@ -14229,7 +14250,7 @@
         <v>LEFT(CAST(PFUNC.DATADEMISSAO AS DATE), 8) AS [Data da Transferência],</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -14254,7 +14275,7 @@
         <v>'' AS [Código do Estabelecimento Origem, cfe. Tabela de Estabelecimentos],</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -14294,17 +14315,17 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14336,7 +14357,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -14367,7 +14388,7 @@
         <v>LEFT(CAST(PFUNC.CODFILIAL AS VARCHAR), 4) AS [Código da Unidade, cfe. Tabela de Unidades],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -14392,7 +14413,7 @@
         <v>'' AS [Código do Contrato],</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8</v>
       </c>
@@ -14423,7 +14444,7 @@
         <v>LEFT(CAST(PFHSTSAL.DTMUDANCA AS DATE), 8) AS [Data da Alteração],</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -14445,7 +14466,7 @@
         <v>'' AS [Tipo de Salário],</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -14464,7 +14485,7 @@
         <v>'' AS [1 – Mensal],</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>7</v>
       </c>
@@ -14483,7 +14504,7 @@
         <v>'' AS [2 – Por Quinzena],</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -14502,7 +14523,7 @@
         <v>'' AS [3 – Por Semana],</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -14521,7 +14542,7 @@
         <v>'' AS [4 – Por Dia],</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>7</v>
       </c>
@@ -14540,7 +14561,7 @@
         <v>'' AS [5 – Por Hora],</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -14559,7 +14580,7 @@
         <v>'' AS [6 – Por Tarefa],</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>7</v>
       </c>
@@ -14578,7 +14599,7 @@
         <v>'' AS [7 – Outros],</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -14612,7 +14633,7 @@
         <v>LEFT(CAST(PFUNC.SALARIO AS DECIMAL(11,2)), 11) AS [Salário Contratual, cfe. Tipo de Salário],</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
@@ -14648,7 +14669,7 @@
 de horistas (tipo de salário “5”).],</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>8</v>
       </c>
@@ -14673,7 +14694,7 @@
         <v>'' AS [Código do Cargo, cfe. Tabela de Cargos],</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
@@ -14695,7 +14716,7 @@
         <v>'' AS [Motivo de Alteração Salarial, cfe. Tabela de Motivos de Reajustes Salariais],</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
@@ -14717,7 +14738,7 @@
         <v>'' AS [Tipo de Salário Anterior (Se não houve alteração repita a informação atual)],</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>11</v>
       </c>
@@ -14748,7 +14769,7 @@
         <v>LEFT(CAST(PFHSTSAL.SALARIO AS INTEGER), 11) AS [Salário Contratual Anterior (Se não houve alteração repita a informação atual) ],</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5</v>
       </c>
@@ -14779,7 +14800,7 @@
         <v>LEFT(CAST(PFHSTSAL.JORNADA AS INTEGER), 5) AS [Horas Contatuais Anterior (Se não houve alteração repita a informação atual) ],</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>8</v>
       </c>
@@ -14816,16 +14837,16 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14857,7 +14878,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -14888,7 +14909,7 @@
         <v>LEFT(CAST(PFUNC.CODFILIAL AS VARCHAR), 4) AS [Código da Unidade, cfe. Tabela de Unidades],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -14912,7 +14933,7 @@
         <v>'' AS [Código do Contrato],</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8</v>
       </c>
@@ -14943,7 +14964,7 @@
         <v>LEFT(CAST(PFUFERIASPER.DATAINICIO AS DATE), 8) AS [Data de Início de Gozo das Férias],</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>8</v>
       </c>
@@ -14974,7 +14995,7 @@
         <v>LEFT(CAST(PFUFERIASPER.DATAFIM AS DATE), 8) AS [Data de Término de Gozo das Férias],</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8</v>
       </c>
@@ -15005,7 +15026,7 @@
         <v>LEFT(CAST(PFUFERIAS.INICIOPERAQUIS AS DATE), 8) AS [Data de Início do Período Aquisitivo],</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>8</v>
       </c>
@@ -15036,7 +15057,7 @@
         <v>LEFT(CAST(PFUFERIAS.FIMPERAQUIS AS DATE), 8) AS [Data de Término do Período Aquisitivo],</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -15070,7 +15091,7 @@
         <v>LEFT(CAST(PFUFERIASPER.NRODIASFERIAS AS DECIMAL(10,2)), 4) AS [Dias de Férias Cedidos],</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>4</v>
       </c>
@@ -15118,18 +15139,18 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="53.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15161,7 +15182,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -15195,7 +15216,7 @@
         <v>LEFT(CAST(PFDEPEND.CODCOLIGADA AS VARCHAR), 4) AS [Código da Empresa, cfe. Tabela de Empresas],</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -15229,7 +15250,7 @@
         <v>LEFT(CAST(PFUNC.CODPESSOA AS INTEGER), 8) AS [Código da Pessoa],</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -15263,7 +15284,7 @@
         <v>LEFT(CAST(PFDEPEND.NRODEPEND AS INTEGER), 2) AS [Familiar (Número Sequencial), iniciando em “01” a cada Pessoa],</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>40</v>
       </c>
@@ -15297,7 +15318,7 @@
         <v>LEFT(CAST(PFDEPEND.NOME AS VARCHAR), 40) AS [Nome do Familiar],</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8</v>
       </c>
@@ -15331,7 +15352,7 @@
         <v>LEFT(CAST(PFDEPEND.DTNASCIMENTO AS DATE), 8) AS [Data de Nascimento],</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>20</v>
       </c>
@@ -15356,7 +15377,7 @@
         <v>'' AS [Local de Nascimento],</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
@@ -15381,7 +15402,7 @@
         <v>'' AS [UF do Nascimento],</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -15414,7 +15435,7 @@
         <v>LEFT(CAST(PFDEPEND.SEXO AS VARCHAR), 1) AS [Sexo],</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>7</v>
       </c>
@@ -15428,7 +15449,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -15442,7 +15463,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1</v>
       </c>
@@ -15476,7 +15497,7 @@
         <v>LEFT(CAST(PFDEPEND.GRAUPARENTESCO AS VARCHAR), 1) AS [Grau de Parentesco:],</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>7</v>
       </c>
@@ -15494,7 +15515,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>7</v>
       </c>
@@ -15512,7 +15533,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>7</v>
       </c>
@@ -15530,7 +15551,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>7</v>
       </c>
@@ -15548,7 +15569,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>7</v>
       </c>
@@ -15566,7 +15587,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>7</v>
       </c>
@@ -15584,7 +15605,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>7</v>
       </c>
@@ -15602,7 +15623,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>7</v>
       </c>
@@ -15620,7 +15641,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>7</v>
       </c>
@@ -15638,7 +15659,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>7</v>
       </c>
@@ -15656,7 +15677,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>7</v>
       </c>
@@ -15674,7 +15695,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>7</v>
       </c>
@@ -15692,7 +15713,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>7</v>
       </c>
@@ -15710,7 +15731,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
@@ -15735,7 +15756,7 @@
         <v>'0' AS [Grau de Dependência:],</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>7</v>
       </c>
@@ -15753,7 +15774,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>7</v>
       </c>
@@ -15771,7 +15792,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>7</v>
       </c>
@@ -15789,7 +15810,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>7</v>
       </c>
@@ -15807,7 +15828,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>7</v>
       </c>
@@ -15825,7 +15846,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>7</v>
       </c>
@@ -15843,7 +15864,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>7</v>
       </c>
@@ -15861,7 +15882,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1</v>
       </c>
@@ -15895,7 +15916,7 @@
         <v>LEFT(CAST(PFDEPEND.INCSALFAM AS VARCHAR), 1) AS [Dependente para Salário Família:],</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>7</v>
       </c>
@@ -15913,7 +15934,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>7</v>
       </c>
@@ -15931,7 +15952,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1</v>
       </c>
@@ -15965,7 +15986,7 @@
         <v>LEFT(CAST(PFDEPEND.INCIRRF AS VARCHAR), 1) AS [Dependente para o IRF:],</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>7</v>
       </c>
@@ -15983,7 +16004,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>7</v>
       </c>
@@ -16001,7 +16022,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1</v>
       </c>
@@ -16026,7 +16047,7 @@
         <v>'N' AS [Dependente do Auxílio Creche:],</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>7</v>
       </c>
@@ -16040,7 +16061,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>7</v>
       </c>
@@ -16054,7 +16075,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>10</v>
       </c>
@@ -16079,7 +16100,7 @@
         <v>'' AS [Cartório do Registro de Nascimento],</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>10</v>
       </c>
@@ -16104,7 +16125,7 @@
         <v>'' AS [Número do Registro de Nascimento],</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>5</v>
       </c>
@@ -16129,7 +16150,7 @@
         <v>'' AS [Livro do Registro de Nascimento],</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>5</v>
       </c>
@@ -16154,7 +16175,7 @@
         <v>'' AS [Página do Registro de Nascimento],</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>8</v>
       </c>
@@ -16179,7 +16200,7 @@
         <v>'' AS [Data da Entrega da Certidão de Nascimento],</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>8</v>
       </c>
@@ -16204,7 +16225,7 @@
         <v>'' AS [Data da Baixa da Certidão de Nascimento],</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2</v>
       </c>
@@ -16229,7 +16250,7 @@
         <v>'' AS [Estado Civil:],</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>7</v>
       </c>
@@ -16247,7 +16268,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>7</v>
       </c>
@@ -16265,7 +16286,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>7</v>
       </c>
@@ -16283,7 +16304,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>7</v>
       </c>
@@ -16301,7 +16322,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>7</v>
       </c>
@@ -16319,7 +16340,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>7</v>
       </c>
@@ -16337,7 +16358,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>7</v>
       </c>
@@ -16355,7 +16376,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>7</v>
       </c>
@@ -16373,7 +16394,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>11</v>
       </c>
@@ -16398,7 +16419,7 @@
         <v>'' AS [CPF],</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2</v>
       </c>
@@ -16423,7 +16444,7 @@
         <v>'' AS [Grau de Instrução],</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>7</v>
       </c>
@@ -16441,7 +16462,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>7</v>
       </c>
@@ -16459,7 +16480,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>7</v>
       </c>
@@ -16477,7 +16498,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>7</v>
       </c>
@@ -16495,7 +16516,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>7</v>
       </c>
@@ -16513,7 +16534,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>7</v>
       </c>
@@ -16531,7 +16552,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>7</v>
       </c>
@@ -16549,7 +16570,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>7</v>
       </c>
@@ -16567,7 +16588,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>7</v>
       </c>
@@ -16585,7 +16606,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>7</v>
       </c>
@@ -16603,7 +16624,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>7</v>
       </c>
@@ -16621,7 +16642,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>7</v>
       </c>
@@ -16639,7 +16660,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>7</v>
       </c>
@@ -16657,7 +16678,7 @@
         <v>'' AS ,</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>20</v>
       </c>
@@ -16682,7 +16703,7 @@
         <v>'' AS [Número do Cartão do SUS],</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>70</v>
       </c>

--- a/DICIONARIO DE DADOS.xlsx
+++ b/DICIONARIO DE DADOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0-Repositorios\sql-migracao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410C7918-B35C-48D0-9175-FFB6C19CE284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348A2293-5950-474A-968C-D2C7874C5D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="920" firstSheet="1" activeTab="6" xr2:uid="{365E4779-0F30-4366-ADA5-894CEE121BCE}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="920" firstSheet="1" activeTab="6" xr2:uid="{365E4779-0F30-4366-ADA5-894CEE121BCE}"/>
   </bookViews>
   <sheets>
     <sheet name="ALT CADASTRAIS" sheetId="12" r:id="rId1"/>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2331" uniqueCount="858">
   <si>
     <t>TM</t>
   </si>
@@ -7755,7 +7755,7 @@
       <c r="F54" s="10"/>
       <c r="G54" s="11"/>
     </row>
-    <row r="55" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>12</v>
       </c>
@@ -11685,9 +11685,18 @@
         <f>"["&amp;E2&amp;"]"</f>
         <v>[Código da Empresa, cfe. Tabela de Empresas]</v>
       </c>
+      <c r="G2" t="s">
+        <v>328</v>
+      </c>
+      <c r="H2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I2" t="s">
+        <v>783</v>
+      </c>
       <c r="J2" t="str">
-        <f t="shared" ref="J2" si="0">"'' AS "&amp;F2&amp;","</f>
-        <v>'' AS [Código da Empresa, cfe. Tabela de Empresas],</v>
+        <f t="shared" ref="J2" si="0">"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
+        <v>LEFT(CAST(PFUNC.CODCOLIGADA AS VARCHAR), 4) AS [Código da Empresa, cfe. Tabela de Empresas],</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -15127,8 +15136,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/DICIONARIO DE DADOS.xlsx
+++ b/DICIONARIO DE DADOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0-Repositorios\sql-migracao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348A2293-5950-474A-968C-D2C7874C5D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66C104B-F1EF-4874-92E6-8EFB8440DEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="920" firstSheet="1" activeTab="6" xr2:uid="{365E4779-0F30-4366-ADA5-894CEE121BCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="920" xr2:uid="{365E4779-0F30-4366-ADA5-894CEE121BCE}"/>
   </bookViews>
   <sheets>
     <sheet name="ALT CADASTRAIS" sheetId="12" r:id="rId1"/>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2331" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="858">
   <si>
     <t>TM</t>
   </si>
@@ -848,9 +848,6 @@
     <t>Data da Alteração</t>
   </si>
   <si>
-    <t>Variável:</t>
-  </si>
-  <si>
     <t>CCON – Código do Contrato</t>
   </si>
   <si>
@@ -862,15 +859,6 @@
   <si>
     <t>Novo Conteúdo. Descrição do Novo Código na época da
 alteração. Caso não seja informada, será gravada a atual.</t>
-  </si>
-  <si>
-    <t>Código Antigo, cfe. Variável acima. OBS.: Campo obrigatório nas
-conversões para o Darwin.</t>
-  </si>
-  <si>
-    <t>Conteúdo Antigo. Descrição do Código Antigo na época da
-alteração. Caso não seja informada, será gravada a atual. OBS.:
-Campo obrigatório nas conversões para o Darwin.</t>
   </si>
   <si>
     <t>Data de Início de Gozo das Férias</t>
@@ -3254,6 +3242,18 @@
   </si>
   <si>
     <t>CODSECAO</t>
+  </si>
+  <si>
+    <t>Variável</t>
+  </si>
+  <si>
+    <t>Código Antigo, cfe. Variável acima. OBS. Campo obrigatório nas
+conversões para o Darwin.</t>
+  </si>
+  <si>
+    <t>Conteúdo Antigo. Descrição do Código Antigo na época da
+alteração. Caso não seja informada, será gravada a atual. OBS.
+Campo obrigatório nas conversões para o Darwin.</t>
   </si>
 </sst>
 </file>
@@ -3385,7 +3385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3433,6 +3433,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4234,16 +4237,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>322</v>
-      </c>
       <c r="I1" t="s">
-        <v>326</v>
+        <v>319</v>
+      </c>
+      <c r="J1" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -4267,8 +4273,8 @@
         <v>[Código da Unidade, cfe. Tabela de Unidades]</v>
       </c>
       <c r="J2" t="str">
-        <f>"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
-        <v>LEFT(CAST(. AS ), 4) AS [Código da Unidade, cfe. Tabela de Unidades],</v>
+        <f t="shared" ref="J2:J11" si="0">"'' AS "&amp;F2&amp;","</f>
+        <v>'' AS [Código da Unidade, cfe. Tabela de Unidades],</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -4287,6 +4293,14 @@
       <c r="E3" t="s">
         <v>18</v>
       </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F11" si="1">"["&amp;E3&amp;"]"</f>
+        <v>[Código do Contrato]</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" si="0"/>
+        <v>'' AS [Código do Contrato],</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -4304,6 +4318,14 @@
       <c r="E4" t="s">
         <v>241</v>
       </c>
+      <c r="F4" t="str">
+        <f t="shared" si="1"/>
+        <v>[Data da Alteração]</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>'' AS [Data da Alteração],</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -4319,7 +4341,15 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>242</v>
+        <v>855</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="1"/>
+        <v>[Variável]</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>'' AS [Variável],</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -4333,7 +4363,15 @@
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>243</v>
+        <v>242</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="1"/>
+        <v>[CCON – Código do Contrato]</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>'' AS [CCON – Código do Contrato],</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -4347,7 +4385,15 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>244</v>
+        <v>243</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="1"/>
+        <v>[TADM – Tipo de Admissão (admissão, transferência de entrada)]</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>'' AS [TADM – Tipo de Admissão (admissão, transferência de entrada)],</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -4364,7 +4410,15 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>245</v>
+        <v>244</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="1"/>
+        <v>[Novo Código, cfe. Variável acima]</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>'' AS [Novo Código, cfe. Variável acima],</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -4381,7 +4435,17 @@
         <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>246</v>
+        <v>245</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
+        <v>[Novo Conteúdo. Descrição do Novo Código na época da
+alteração. Caso não seja informada, será gravada a atual.]</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>'' AS [Novo Conteúdo. Descrição do Novo Código na época da
+alteração. Caso não seja informada, será gravada a atual.],</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -4397,8 +4461,18 @@
       <c r="D10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
-        <v>247</v>
+      <c r="E10" s="21" t="s">
+        <v>856</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v>[Código Antigo, cfe. Variável acima. OBS. Campo obrigatório nas
+conversões para o Darwin.]</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>'' AS [Código Antigo, cfe. Variável acima. OBS. Campo obrigatório nas
+conversões para o Darwin.],</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -4414,14 +4488,27 @@
       <c r="D11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
-        <v>248</v>
+      <c r="E11" s="21" t="s">
+        <v>857</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="1"/>
+        <v>[Conteúdo Antigo. Descrição do Código Antigo na época da
+alteração. Caso não seja informada, será gravada a atual. OBS.
+Campo obrigatório nas conversões para o Darwin.]</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="0"/>
+        <v>'' AS [Conteúdo Antigo. Descrição do Código Antigo na época da
+alteração. Caso não seja informada, será gravada a atual. OBS.
+Campo obrigatório nas conversões para o Darwin.],</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4460,22 +4547,22 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>324</v>
-      </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -4496,13 +4583,13 @@
         <v>[Código da Empresa, cfe. Tabela de Empresas]</v>
       </c>
       <c r="G2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J5" si="0">"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
@@ -4527,10 +4614,10 @@
         <v>[Código do Estabelecimento Atual, cfe. Tabela de Estabelecimentos]</v>
       </c>
       <c r="H3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I3" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="0"/>
@@ -4555,13 +4642,13 @@
         <v>[Código da Unidade, cfe. Tabela de Unidades]</v>
       </c>
       <c r="G4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H4" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I4" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="0"/>
@@ -4586,13 +4673,13 @@
         <v>[Código do Contrato]</v>
       </c>
       <c r="G5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I5" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="0"/>
@@ -4617,13 +4704,13 @@
         <v>[Código da Pessoa, cfe. Tabela de Pessoas]</v>
       </c>
       <c r="G6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I6" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" ref="J6:J12" si="2">"LEFT(CAST("&amp;H6&amp;"."&amp;I6&amp;" AS "&amp;G6&amp;"), "&amp;A6*1&amp;") AS "&amp;F6&amp;","</f>
@@ -4641,20 +4728,20 @@
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="1"/>
         <v>[Situação:]</v>
       </c>
       <c r="G7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="2"/>
@@ -4755,13 +4842,13 @@
         <v>[Data de Admissão]</v>
       </c>
       <c r="G12" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H12" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I12" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="2"/>
@@ -4779,20 +4866,20 @@
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
         <v>[Tipo de Salário:]</v>
       </c>
       <c r="G13" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H13" t="s">
+        <v>376</v>
+      </c>
+      <c r="I13" t="s">
         <v>379</v>
-      </c>
-      <c r="I13" t="s">
-        <v>382</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" ref="J13" si="3">"LEFT(CAST("&amp;H13&amp;"."&amp;I13&amp;" AS "&amp;G13&amp;"), "&amp;A13*1&amp;") AS "&amp;F13&amp;","</f>
@@ -5017,7 +5104,7 @@
         <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="1"/>
@@ -5217,13 +5304,13 @@
         <v>[Número do Banco do Funcionário (Banco Central)]</v>
       </c>
       <c r="G35" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H35" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I35" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="J35" t="str">
         <f t="shared" ref="J35:J38" si="5">"LEFT(CAST("&amp;H35&amp;"."&amp;I35&amp;" AS "&amp;G35&amp;"), "&amp;A35*1&amp;") AS "&amp;F35&amp;","</f>
@@ -5248,13 +5335,13 @@
         <v>[Agencia Bancária do Funcionário]</v>
       </c>
       <c r="G36" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H36" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I36" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="J36" t="str">
         <f t="shared" si="5"/>
@@ -5279,13 +5366,13 @@
         <v>[Dígito da Agência Bancária do Funcionário]</v>
       </c>
       <c r="G37" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H37" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I37" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="J37" t="str">
         <f t="shared" si="5"/>
@@ -5310,13 +5397,13 @@
         <v>[Número/Dígito da Conta Corrente]</v>
       </c>
       <c r="G38" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H38" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I38" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="J38" t="str">
         <f t="shared" si="5"/>
@@ -5495,13 +5582,13 @@
         <v>[Data da Rescisão]</v>
       </c>
       <c r="G46" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H46" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I46" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="J46" t="str">
         <f t="shared" ref="J46:J48" si="7">"LEFT(CAST("&amp;H46&amp;"."&amp;I46&amp;" AS "&amp;G46&amp;"), "&amp;A46*1&amp;") AS "&amp;F46&amp;","</f>
@@ -5548,13 +5635,13 @@
         <v>[Matrícula para o eSocial]</v>
       </c>
       <c r="G48" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H48" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I48" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="J48" t="str">
         <f t="shared" si="7"/>
@@ -6251,7 +6338,7 @@
         <v>7</v>
       </c>
       <c r="E93" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F93" t="str">
         <f t="shared" si="8"/>
@@ -6266,7 +6353,7 @@
         <v>7</v>
       </c>
       <c r="E94" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F94" t="str">
         <f t="shared" si="8"/>
@@ -6281,7 +6368,7 @@
         <v>7</v>
       </c>
       <c r="E95" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F95" t="str">
         <f t="shared" si="8"/>
@@ -6296,7 +6383,7 @@
         <v>7</v>
       </c>
       <c r="E96" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F96" t="str">
         <f t="shared" si="8"/>
@@ -6311,7 +6398,7 @@
         <v>7</v>
       </c>
       <c r="E97" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F97" t="str">
         <f t="shared" si="8"/>
@@ -6329,20 +6416,20 @@
         <v>8</v>
       </c>
       <c r="E98" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="F98" t="str">
         <f t="shared" si="8"/>
         <v>[Vínculo Empregatício:]</v>
       </c>
       <c r="G98" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H98" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I98" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="J98" t="str">
         <f t="shared" ref="J98:J139" si="9">"LEFT(CAST("&amp;H98&amp;"."&amp;I98&amp;" AS "&amp;G98&amp;"), "&amp;A98*1&amp;") AS "&amp;F98&amp;","</f>
@@ -6351,7 +6438,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E99" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F99" t="str">
         <f t="shared" si="8"/>
@@ -6370,7 +6457,7 @@
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F100" t="str">
         <f t="shared" si="8"/>
@@ -6391,7 +6478,7 @@
         <v>7</v>
       </c>
       <c r="E101" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F101" t="str">
         <f t="shared" si="8"/>
@@ -6410,7 +6497,7 @@
         <v>7</v>
       </c>
       <c r="E102" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F102" t="str">
         <f t="shared" si="8"/>
@@ -6431,7 +6518,7 @@
         <v>7</v>
       </c>
       <c r="E103" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F103" t="str">
         <f t="shared" si="8"/>
@@ -6450,7 +6537,7 @@
         <v>7</v>
       </c>
       <c r="E104" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F104" t="str">
         <f t="shared" si="8"/>
@@ -6463,7 +6550,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E105" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F105" t="str">
         <f t="shared" si="8"/>
@@ -6482,7 +6569,7 @@
         <v>7</v>
       </c>
       <c r="E106" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F106" t="str">
         <f t="shared" si="8"/>
@@ -6495,7 +6582,7 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E107" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F107" t="str">
         <f t="shared" si="8"/>
@@ -6508,7 +6595,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E108" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F108" t="str">
         <f t="shared" si="8"/>
@@ -6527,7 +6614,7 @@
         <v>7</v>
       </c>
       <c r="E109" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F109" t="str">
         <f t="shared" si="8"/>
@@ -6542,7 +6629,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E110" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F110" t="str">
         <f t="shared" si="8"/>
@@ -6561,7 +6648,7 @@
         <v>7</v>
       </c>
       <c r="E111" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F111" t="str">
         <f t="shared" si="8"/>
@@ -6582,7 +6669,7 @@
         <v>7</v>
       </c>
       <c r="E112" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F112" t="str">
         <f t="shared" si="8"/>
@@ -6605,7 +6692,7 @@
         <v>7</v>
       </c>
       <c r="E113" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F113" t="str">
         <f t="shared" si="8"/>
@@ -6628,7 +6715,7 @@
         <v>7</v>
       </c>
       <c r="E114" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F114" t="str">
         <f t="shared" si="8"/>
@@ -6651,7 +6738,7 @@
         <v>7</v>
       </c>
       <c r="E115" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F115" t="str">
         <f t="shared" si="8"/>
@@ -6672,7 +6759,7 @@
         <v>7</v>
       </c>
       <c r="E116" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F116" t="str">
         <f t="shared" si="8"/>
@@ -6693,7 +6780,7 @@
         <v>7</v>
       </c>
       <c r="E117" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F117" t="str">
         <f t="shared" si="8"/>
@@ -6716,7 +6803,7 @@
         <v>7</v>
       </c>
       <c r="E118" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F118" t="str">
         <f t="shared" si="8"/>
@@ -6729,7 +6816,7 @@
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E119" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F119" t="str">
         <f t="shared" si="8"/>
@@ -6742,7 +6829,7 @@
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E120" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F120" t="str">
         <f t="shared" si="8"/>
@@ -6761,7 +6848,7 @@
         <v>7</v>
       </c>
       <c r="E121" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F121" t="str">
         <f t="shared" si="8"/>
@@ -6774,7 +6861,7 @@
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E122" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F122" t="str">
         <f t="shared" si="8"/>
@@ -6793,7 +6880,7 @@
         <v>7</v>
       </c>
       <c r="E123" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F123" t="str">
         <f t="shared" si="8"/>
@@ -6806,7 +6893,7 @@
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E124" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F124" t="str">
         <f t="shared" si="8"/>
@@ -6825,7 +6912,7 @@
         <v>7</v>
       </c>
       <c r="E125" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F125" t="str">
         <f t="shared" si="8"/>
@@ -6838,7 +6925,7 @@
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E126" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F126" t="str">
         <f t="shared" si="8"/>
@@ -6853,7 +6940,7 @@
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E127" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F127" t="str">
         <f t="shared" si="8"/>
@@ -7224,19 +7311,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>324</v>
-      </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -7260,13 +7347,13 @@
         <v>[Código do Cargo]</v>
       </c>
       <c r="G2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J2" t="str">
         <f>"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
@@ -7294,13 +7381,13 @@
         <v>[Descrição do Cargo]</v>
       </c>
       <c r="G3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I3" t="s">
         <v>328</v>
-      </c>
-      <c r="H3" t="s">
-        <v>323</v>
-      </c>
-      <c r="I3" t="s">
-        <v>331</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" ref="J3:J4" si="1">"LEFT(CAST("&amp;H3&amp;"."&amp;I3&amp;" AS "&amp;G3&amp;"), "&amp;A3*1&amp;") AS "&amp;F3&amp;","</f>
@@ -7328,13 +7415,13 @@
         <v>[CBO]</v>
       </c>
       <c r="G4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -7362,7 +7449,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -7370,7 +7457,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -7378,7 +7465,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -7386,7 +7473,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -7394,7 +7481,7 @@
         <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -7402,7 +7489,7 @@
         <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -7410,7 +7497,7 @@
         <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -7418,7 +7505,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -7426,7 +7513,7 @@
         <v>51</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -7434,7 +7521,7 @@
         <v>52</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -7442,7 +7529,7 @@
         <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -7450,7 +7537,7 @@
         <v>71</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -7458,7 +7545,7 @@
         <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -7466,7 +7553,7 @@
         <v>91</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -7474,7 +7561,7 @@
         <v>92</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -7482,7 +7569,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -7490,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -7498,7 +7585,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -7506,7 +7593,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -7514,12 +7601,12 @@
         <v>3</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -7527,7 +7614,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -7535,7 +7622,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -7543,7 +7630,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -7551,12 +7638,12 @@
         <v>4</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -7564,7 +7651,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -7572,7 +7659,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -7580,7 +7667,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -7588,7 +7675,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -7596,7 +7683,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -7604,7 +7691,7 @@
         <v>6</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -7612,89 +7699,89 @@
         <v>7</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
@@ -7705,10 +7792,10 @@
     </row>
     <row r="51" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C51" s="13"/>
       <c r="D51" s="10"/>
@@ -7718,10 +7805,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C52" s="13"/>
       <c r="D52" s="10"/>
@@ -7731,10 +7818,10 @@
     </row>
     <row r="53" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C53" s="13"/>
       <c r="D53" s="10"/>
@@ -7744,10 +7831,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C54" s="13"/>
       <c r="D54" s="10"/>
@@ -7755,12 +7842,12 @@
       <c r="F54" s="10"/>
       <c r="G54" s="11"/>
     </row>
-    <row r="55" spans="1:7" ht="27" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>12</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C55" s="13"/>
       <c r="D55" s="10"/>
@@ -7770,10 +7857,10 @@
     </row>
     <row r="56" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C56" s="13"/>
       <c r="D56" s="10"/>
@@ -7786,7 +7873,7 @@
         <v>5</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C57" s="13"/>
       <c r="D57" s="10"/>
@@ -7796,10 +7883,10 @@
     </row>
     <row r="58" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C58" s="13"/>
       <c r="D58" s="10"/>
@@ -7809,10 +7896,10 @@
     </row>
     <row r="59" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C59" s="13"/>
       <c r="D59" s="10"/>
@@ -7822,10 +7909,10 @@
     </row>
     <row r="60" spans="1:7" ht="54" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C60" s="13"/>
       <c r="D60" s="10"/>
@@ -7835,10 +7922,10 @@
     </row>
     <row r="61" spans="1:7" ht="54" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C61" s="13"/>
       <c r="D61" s="10"/>
@@ -7848,10 +7935,10 @@
     </row>
     <row r="62" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C62" s="13"/>
       <c r="D62" s="10"/>
@@ -7861,10 +7948,10 @@
     </row>
     <row r="63" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C63" s="13"/>
       <c r="D63" s="10"/>
@@ -7874,10 +7961,10 @@
     </row>
     <row r="64" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C64" s="13"/>
       <c r="D64" s="10"/>
@@ -7887,10 +7974,10 @@
     </row>
     <row r="65" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C65" s="13"/>
       <c r="D65" s="10"/>
@@ -7900,10 +7987,10 @@
     </row>
     <row r="66" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C66" s="13"/>
       <c r="D66" s="10"/>
@@ -7913,10 +8000,10 @@
     </row>
     <row r="67" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A67" s="12" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C67" s="13"/>
       <c r="D67" s="10"/>
@@ -7926,10 +8013,10 @@
     </row>
     <row r="68" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A68" s="12" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C68" s="13"/>
       <c r="D68" s="10"/>
@@ -7939,10 +8026,10 @@
     </row>
     <row r="69" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C69" s="13"/>
       <c r="D69" s="10"/>
@@ -7952,10 +8039,10 @@
     </row>
     <row r="70" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C70" s="13"/>
       <c r="D70" s="10"/>
@@ -7965,10 +8052,10 @@
     </row>
     <row r="71" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A71" s="12" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C71" s="13"/>
       <c r="D71" s="10"/>
@@ -7978,10 +8065,10 @@
     </row>
     <row r="72" spans="1:7" ht="54" x14ac:dyDescent="0.2">
       <c r="A72" s="12" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C72" s="13"/>
       <c r="D72" s="10"/>
@@ -7991,10 +8078,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C73" s="13"/>
       <c r="D73" s="10"/>
@@ -8004,10 +8091,10 @@
     </row>
     <row r="74" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C74" s="13"/>
       <c r="D74" s="10"/>
@@ -8017,10 +8104,10 @@
     </row>
     <row r="75" spans="1:7" ht="27" x14ac:dyDescent="0.2">
       <c r="A75" s="12" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C75" s="13"/>
       <c r="D75" s="10"/>
@@ -8030,10 +8117,10 @@
     </row>
     <row r="76" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A76" s="12" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C76" s="13"/>
       <c r="D76" s="10"/>
@@ -8043,10 +8130,10 @@
     </row>
     <row r="77" spans="1:7" ht="54" x14ac:dyDescent="0.2">
       <c r="A77" s="12" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C77" s="13"/>
       <c r="D77" s="10"/>
@@ -8056,10 +8143,10 @@
     </row>
     <row r="78" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A78" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C78" s="13"/>
       <c r="D78" s="10"/>
@@ -8069,10 +8156,10 @@
     </row>
     <row r="79" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A79" s="12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C79" s="13"/>
       <c r="D79" s="10"/>
@@ -8082,10 +8169,10 @@
     </row>
     <row r="80" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A80" s="12" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C80" s="13"/>
       <c r="D80" s="10"/>
@@ -8100,15 +8187,15 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="14" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -8116,12 +8203,12 @@
         <v>1</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -8129,7 +8216,7 @@
         <v>0</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -8137,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -8145,7 +8232,7 @@
         <v>2</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -8153,7 +8240,7 @@
         <v>3</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -8161,7 +8248,7 @@
         <v>4</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
@@ -8169,7 +8256,7 @@
         <v>5</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -8177,7 +8264,7 @@
         <v>6</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
@@ -8185,7 +8272,7 @@
         <v>7</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
@@ -8193,23 +8280,23 @@
         <v>9</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
@@ -8217,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
@@ -8225,12 +8312,12 @@
         <v>2</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -8238,7 +8325,7 @@
         <v>0</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
@@ -8246,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
@@ -8254,7 +8341,7 @@
         <v>2</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
@@ -8262,7 +8349,7 @@
         <v>3</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
@@ -8270,7 +8357,7 @@
         <v>4</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
@@ -8278,7 +8365,7 @@
         <v>5</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
@@ -8286,17 +8373,17 @@
         <v>6</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>8</v>
@@ -8312,7 +8399,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
@@ -8320,7 +8407,7 @@
         <v>1</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
@@ -8328,7 +8415,7 @@
         <v>2</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
@@ -8336,7 +8423,7 @@
         <v>3</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
@@ -8344,7 +8431,7 @@
         <v>4</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
@@ -8352,12 +8439,12 @@
         <v>5</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
@@ -8365,7 +8452,7 @@
         <v>1</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
@@ -8373,7 +8460,7 @@
         <v>2</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
@@ -8381,7 +8468,7 @@
         <v>3</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
@@ -8389,7 +8476,7 @@
         <v>4</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
@@ -8397,7 +8484,7 @@
         <v>5</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
@@ -8405,7 +8492,7 @@
         <v>6</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
@@ -8413,7 +8500,7 @@
         <v>7</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
@@ -8421,7 +8508,7 @@
         <v>9</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
@@ -8429,7 +8516,7 @@
         <v>10</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
@@ -8437,7 +8524,7 @@
         <v>11</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
@@ -8445,7 +8532,7 @@
         <v>12</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
@@ -8453,12 +8540,12 @@
         <v>13</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
@@ -8466,7 +8553,7 @@
         <v>1</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
@@ -8474,7 +8561,7 @@
         <v>2</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
@@ -8482,7 +8569,7 @@
         <v>4</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
@@ -8490,7 +8577,7 @@
         <v>6</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
@@ -8498,7 +8585,7 @@
         <v>8</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
@@ -8506,12 +8593,12 @@
         <v>9</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
@@ -8519,7 +8606,7 @@
         <v>0</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
@@ -8527,7 +8614,7 @@
         <v>1</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
@@ -8535,7 +8622,7 @@
         <v>2</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
@@ -8543,7 +8630,7 @@
         <v>3</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
@@ -8551,7 +8638,7 @@
         <v>4</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
@@ -8559,12 +8646,12 @@
         <v>5</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
@@ -8572,7 +8659,7 @@
         <v>0</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
@@ -8580,7 +8667,7 @@
         <v>1</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
@@ -8590,287 +8677,287 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" s="14" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="14" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" s="14" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" s="14" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" s="14" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" s="14" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="14" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" s="14" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" s="14" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" s="14" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" s="14" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" s="14" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" s="14" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" s="14" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" s="14" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" s="14" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" s="14" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" s="14" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" s="14" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" s="14" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="14" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" s="14" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" s="14" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" s="14" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" s="14" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" s="14" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" s="14" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" s="16" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" s="16" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" s="16" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" s="16" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" s="16" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" s="16" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" s="16" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" s="16" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
@@ -8878,7 +8965,7 @@
         <v>90</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
@@ -8886,7 +8973,7 @@
         <v>97</v>
       </c>
       <c r="B194" s="15" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
@@ -8894,7 +8981,7 @@
         <v>98</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
@@ -8902,12 +8989,12 @@
         <v>99</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
@@ -8915,7 +9002,7 @@
         <v>10</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
@@ -8923,7 +9010,7 @@
         <v>20</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
@@ -8931,7 +9018,7 @@
         <v>21</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
@@ -8939,7 +9026,7 @@
         <v>22</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
@@ -8947,7 +9034,7 @@
         <v>23</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
@@ -8955,7 +9042,7 @@
         <v>24</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
@@ -8963,7 +9050,7 @@
         <v>25</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
@@ -8971,7 +9058,7 @@
         <v>26</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
@@ -8979,7 +9066,7 @@
         <v>27</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
@@ -8987,7 +9074,7 @@
         <v>28</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
@@ -8995,7 +9082,7 @@
         <v>29</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -9003,7 +9090,7 @@
         <v>30</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
@@ -9011,7 +9098,7 @@
         <v>31</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
@@ -9019,7 +9106,7 @@
         <v>32</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -9027,7 +9114,7 @@
         <v>34</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
@@ -9035,7 +9122,7 @@
         <v>35</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
@@ -9043,7 +9130,7 @@
         <v>36</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -9051,7 +9138,7 @@
         <v>37</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
@@ -9059,7 +9146,7 @@
         <v>38</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
@@ -9067,7 +9154,7 @@
         <v>39</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
@@ -9075,7 +9162,7 @@
         <v>40</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
@@ -9083,7 +9170,7 @@
         <v>41</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
@@ -9091,7 +9178,7 @@
         <v>42</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
@@ -9099,7 +9186,7 @@
         <v>43</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
@@ -9107,7 +9194,7 @@
         <v>44</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -9115,7 +9202,7 @@
         <v>45</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
@@ -9123,7 +9210,7 @@
         <v>46</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
@@ -9131,7 +9218,7 @@
         <v>47</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
@@ -9139,7 +9226,7 @@
         <v>48</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
@@ -9147,7 +9234,7 @@
         <v>49</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
@@ -9155,7 +9242,7 @@
         <v>50</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
@@ -9163,7 +9250,7 @@
         <v>51</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
@@ -9171,7 +9258,7 @@
         <v>60</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
@@ -9179,7 +9266,7 @@
         <v>61</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
@@ -9187,7 +9274,7 @@
         <v>62</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
@@ -9195,12 +9282,12 @@
         <v>70</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
@@ -9208,7 +9295,7 @@
         <v>1</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
@@ -9216,44 +9303,44 @@
         <v>2</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A242" s="17" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A244" s="17" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="15" x14ac:dyDescent="0.25">
@@ -9261,15 +9348,15 @@
         <v>12</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A246" s="17" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="15" x14ac:dyDescent="0.25">
@@ -9277,175 +9364,175 @@
         <v>5</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A248" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A249" s="17" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A250" s="17" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A251" s="17" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A252" s="17" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A253" s="17" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A254" s="17" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A255" s="17" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A256" s="17" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A257" s="17" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A258" s="17" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="259" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A259" s="17" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="260" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A260" s="17" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="261" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A261" s="17" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="262" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A262" s="17" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="263" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A263" s="17" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A264" s="17" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A265" s="17" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="266" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A266" s="17" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A267" s="17" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A268" s="17" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="15" x14ac:dyDescent="0.25">
@@ -9453,360 +9540,360 @@
         <v>10</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="270" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A270" s="17" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A271" s="17" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="272" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A272" s="17" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A273" s="17" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A274" s="17" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A275" s="17" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A276" s="17" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A277" s="17" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A278" s="17" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A279" s="17" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A280" s="17" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A281" s="17" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A282" s="17" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A283" s="17" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A284" s="17" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A285" s="17" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A288" s="18" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B288" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C288" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A289" s="18" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B289" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C289" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A290" s="18" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B290" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C290" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A291" s="18" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B291" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C291" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A292" s="18" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B292" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C292" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A293" s="18" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B293" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C293" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A294" s="18" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B294" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C294" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A295" s="18" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B295" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C295" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A296" s="18" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B296" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C296" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A297" s="18" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B297" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C297" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A298" s="18" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B298" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C298" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A299" s="18" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B299" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C299" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A300" s="18" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B300" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C300" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A301" s="18" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B301" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C301" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A302" s="18" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B302" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C302" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A303" s="18" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B303" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C303" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A304" s="18" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B304" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C304" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A305" s="18" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B305" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C305" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A306" s="18" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B306" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C306" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A307" s="18" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B307" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C307" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -9814,124 +9901,124 @@
         <v>10</v>
       </c>
       <c r="B308" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C308" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A309" s="18" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B309" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C309" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A310" s="18" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B310" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C310" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A311" s="18" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B311" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C311" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A312" s="18" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B312" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C312" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A313" s="18" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B313" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C313" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A314" s="18" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B314" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C314" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A315" s="18" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B315" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C315" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A316" s="18" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B316" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C316" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="21.75" x14ac:dyDescent="0.2">
       <c r="A319" s="19" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B319" s="20" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C319" s="15"/>
     </row>
     <row r="320" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A320" s="18" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B320" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C320" s="15"/>
     </row>
     <row r="321" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A321" s="18" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B321" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C321" s="15"/>
     </row>
@@ -9978,19 +10065,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>324</v>
-      </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -10011,13 +10098,13 @@
         <v>[Código da Unidade, cfe. Tabela de Unidades]</v>
       </c>
       <c r="G2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="I2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="J2" t="str">
         <f>"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
@@ -10042,13 +10129,13 @@
         <v>[Código do Contrato]</v>
       </c>
       <c r="G3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I3" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="J3" t="str">
         <f>"LEFT(CAST("&amp;H3&amp;"."&amp;I3&amp;" AS "&amp;G3&amp;"), "&amp;A3*1&amp;") AS "&amp;F3&amp;","</f>
@@ -10066,7 +10153,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
@@ -10088,7 +10175,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="0"/>
@@ -10107,7 +10194,7 @@
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" si="0"/>
@@ -10126,7 +10213,7 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
@@ -10145,7 +10232,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
@@ -10164,7 +10251,7 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
@@ -10183,7 +10270,7 @@
         <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
@@ -10202,7 +10289,7 @@
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
@@ -10221,7 +10308,7 @@
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" si="0"/>
@@ -10240,7 +10327,7 @@
         <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
@@ -10259,7 +10346,7 @@
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
@@ -10278,7 +10365,7 @@
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
@@ -10297,7 +10384,7 @@
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
@@ -10316,7 +10403,7 @@
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
@@ -10335,7 +10422,7 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F18" t="str">
         <f t="shared" si="0"/>
@@ -10354,7 +10441,7 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" si="0"/>
@@ -10376,7 +10463,7 @@
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="0"/>
@@ -10398,7 +10485,7 @@
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F21" t="str">
         <f t="shared" si="0"/>
@@ -10420,7 +10507,7 @@
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="F22" t="str">
         <f t="shared" si="0"/>
@@ -10439,7 +10526,7 @@
         <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F23" t="str">
         <f t="shared" si="0"/>
@@ -10458,7 +10545,7 @@
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F24" t="str">
         <f t="shared" si="0"/>
@@ -10477,7 +10564,7 @@
         <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="0"/>
@@ -10496,7 +10583,7 @@
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F26" t="str">
         <f t="shared" si="0"/>
@@ -10521,7 +10608,7 @@
         <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="F27" t="str">
         <f t="shared" si="0"/>
@@ -10546,20 +10633,20 @@
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F28" t="str">
         <f t="shared" si="0"/>
         <v>[Valor]</v>
       </c>
       <c r="G28" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="H28" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="I28" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="J28" t="str">
         <f>"LEFT(CAST("&amp;H28&amp;"."&amp;I28&amp;" AS "&amp;G28&amp;"), "&amp;A28*1&amp;") AS "&amp;F28&amp;","</f>
@@ -10577,7 +10664,7 @@
         <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="F29" t="str">
         <f t="shared" si="0"/>
@@ -10599,7 +10686,7 @@
         <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F30" t="str">
         <f t="shared" si="0"/>
@@ -10651,19 +10738,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>324</v>
-      </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -10712,13 +10799,13 @@
         <v>[Código do Vencimento, Desconto ou Base do sistema de Origem]</v>
       </c>
       <c r="G3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H3" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="I3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J3" t="str">
         <f>"LEFT(CAST("&amp;H3&amp;"."&amp;I3&amp;" AS "&amp;G3&amp;"), "&amp;A3*1&amp;") AS "&amp;F3&amp;","</f>
@@ -10746,13 +10833,13 @@
         <v>[Descrição do VDB]</v>
       </c>
       <c r="G4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H4" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="I4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J4" t="str">
         <f>"LEFT(CAST("&amp;H4&amp;"."&amp;I4&amp;" AS "&amp;G4&amp;"), "&amp;A4*1&amp;") AS "&amp;F4&amp;","</f>
@@ -10773,7 +10860,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="1"/>
@@ -10879,19 +10966,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>324</v>
-      </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -10915,13 +11002,13 @@
         <v>[Código da Unidade, cfe. Tabela de Unidades]</v>
       </c>
       <c r="G2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="I2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="J2" t="str">
         <f>"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
@@ -10974,13 +11061,13 @@
         <v>[Data de Início da Ocorrência]</v>
       </c>
       <c r="G4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H4" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="I4" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="J4" t="str">
         <f>"FORMAT("&amp;H4&amp;"."&amp;I4&amp;", 'ddMMyyyy') AS "&amp;F4&amp;","</f>
@@ -11001,20 +11088,20 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="F5" t="str">
         <f>"["&amp;E5&amp;"]"</f>
         <v>[Ocorrência]</v>
       </c>
       <c r="G5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H5" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="I5" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="J5" t="str">
         <f>"LEFT(CAST("&amp;H5&amp;"."&amp;I5&amp;" AS "&amp;G5&amp;"), "&amp;A5*1&amp;") AS "&amp;F5&amp;","</f>
@@ -11596,13 +11683,13 @@
         <v>[Texto da Ocorrência]</v>
       </c>
       <c r="G36" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H36" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="I36" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="J36" t="str">
         <f>"LEFT(CAST("&amp;H36&amp;"."&amp;I36&amp;" AS "&amp;G36&amp;"), "&amp;A36*1&amp;") AS "&amp;F36&amp;","</f>
@@ -11650,19 +11737,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>324</v>
-      </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -11686,13 +11773,13 @@
         <v>[Código da Empresa, cfe. Tabela de Empresas]</v>
       </c>
       <c r="G2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2" si="0">"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
@@ -11720,13 +11807,13 @@
         <v>[Código da Pessoa]</v>
       </c>
       <c r="G3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H3" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" ref="J3:J39" si="2">"LEFT(CAST("&amp;H3&amp;"."&amp;I3&amp;" AS "&amp;G3&amp;"), "&amp;A3*1&amp;") AS "&amp;F3&amp;","</f>
@@ -11754,13 +11841,13 @@
         <v>[Nome da Pessoa]</v>
       </c>
       <c r="G4" t="s">
+        <v>325</v>
+      </c>
+      <c r="H4" t="s">
+        <v>806</v>
+      </c>
+      <c r="I4" t="s">
         <v>328</v>
-      </c>
-      <c r="H4" t="s">
-        <v>809</v>
-      </c>
-      <c r="I4" t="s">
-        <v>331</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="2"/>
@@ -11838,13 +11925,13 @@
         <v>[Data de Nascimento]</v>
       </c>
       <c r="G7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H7" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I7" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="2"/>
@@ -11872,13 +11959,13 @@
         <v>[Local do Nascimento]</v>
       </c>
       <c r="G8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H8" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I8" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="2"/>
@@ -11906,10 +11993,10 @@
         <v>[UF do Nascimento]</v>
       </c>
       <c r="G9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H9" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I9" t="s">
         <v>149</v>
@@ -11933,20 +12020,20 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="1"/>
         <v>[Sexo]</v>
       </c>
       <c r="G10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H10" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I10" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="2"/>
@@ -12011,20 +12098,20 @@
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
         <v>[Raça/Cor]</v>
       </c>
       <c r="G13" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H13" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I13" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="2"/>
@@ -12177,7 +12264,7 @@
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="1"/>
@@ -12341,13 +12428,13 @@
         <v>[Rua (endereço)]</v>
       </c>
       <c r="G27" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H27" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I27" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="J27" t="str">
         <f t="shared" si="2"/>
@@ -12375,13 +12462,13 @@
         <v>[Número (endereço)]</v>
       </c>
       <c r="G28" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H28" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I28" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="J28" t="str">
         <f t="shared" si="2"/>
@@ -12434,13 +12521,13 @@
         <v>[Bairro]</v>
       </c>
       <c r="G30" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H30" t="s">
+        <v>806</v>
+      </c>
+      <c r="I30" t="s">
         <v>809</v>
-      </c>
-      <c r="I30" t="s">
-        <v>812</v>
       </c>
       <c r="J30" t="str">
         <f t="shared" si="2"/>
@@ -12468,13 +12555,13 @@
         <v>[Cidade]</v>
       </c>
       <c r="G31" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H31" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I31" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="J31" t="str">
         <f t="shared" si="2"/>
@@ -12502,10 +12589,10 @@
         <v>[CEP]</v>
       </c>
       <c r="G32" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H32" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I32" t="s">
         <v>148</v>
@@ -12536,13 +12623,13 @@
         <v>[UF]</v>
       </c>
       <c r="G33" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H33" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I33" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="J33" t="str">
         <f t="shared" si="2"/>
@@ -12595,13 +12682,13 @@
         <v>[Telefone]</v>
       </c>
       <c r="G35" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H35" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I35" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="J35" t="str">
         <f t="shared" si="2"/>
@@ -12629,13 +12716,13 @@
         <v>[Email]</v>
       </c>
       <c r="G36" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H36" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I36" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="J36" t="str">
         <f t="shared" si="2"/>
@@ -12663,13 +12750,13 @@
         <v>[PIS]</v>
       </c>
       <c r="G37" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H37" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I37" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="J37" t="str">
         <f t="shared" si="2"/>
@@ -12722,10 +12809,10 @@
         <v>[CPF]</v>
       </c>
       <c r="G39" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H39" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I39" t="s">
         <v>155</v>
@@ -12756,13 +12843,13 @@
         <v>[Identidade (RE ou RG)]</v>
       </c>
       <c r="G40" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H40" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I40" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="J40" t="str">
         <f t="shared" ref="J40:J46" si="4">"LEFT(CAST("&amp;H40&amp;"."&amp;I40&amp;" AS "&amp;G40&amp;"), "&amp;A40*1&amp;") AS "&amp;F40&amp;","</f>
@@ -12790,13 +12877,13 @@
         <v>[Data da Emissão da Identidade]</v>
       </c>
       <c r="G41" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H41" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I41" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="J41" t="str">
         <f>"FORMAT("&amp;H41&amp;"."&amp;I41&amp;", 'ddMMyyyy') AS "&amp;F41&amp;","</f>
@@ -12824,13 +12911,13 @@
         <v>[Órgão Emissor da Identidade]</v>
       </c>
       <c r="G42" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H42" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I42" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="J42" t="str">
         <f t="shared" si="4"/>
@@ -12858,13 +12945,13 @@
         <v>[UF da Identidade]</v>
       </c>
       <c r="G43" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H43" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I43" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="J43" t="str">
         <f t="shared" si="4"/>
@@ -12892,13 +12979,13 @@
         <v>[Título Eleitoral]</v>
       </c>
       <c r="G44" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H44" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I44" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="J44" t="str">
         <f t="shared" si="4"/>
@@ -12926,13 +13013,13 @@
         <v>[Zona Eleitoral]</v>
       </c>
       <c r="G45" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H45" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I45" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="J45" t="str">
         <f t="shared" si="4"/>
@@ -12960,13 +13047,13 @@
         <v>[Seção Eleitoral]</v>
       </c>
       <c r="G46" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H46" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I46" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="J46" t="str">
         <f t="shared" si="4"/>
@@ -12987,7 +13074,7 @@
         <v>32</v>
       </c>
       <c r="E47" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F47" t="str">
         <f t="shared" si="1"/>
@@ -13081,20 +13168,20 @@
         <v>32</v>
       </c>
       <c r="E51" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F51" t="str">
         <f t="shared" si="1"/>
         <v>[Estado Civil]</v>
       </c>
       <c r="G51" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H51" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I51" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="J51" t="str">
         <f t="shared" ref="J51" si="5">"LEFT(CAST("&amp;H51&amp;"."&amp;I51&amp;" AS "&amp;G51&amp;"), "&amp;A51*1&amp;") AS "&amp;F51&amp;","</f>
@@ -13225,20 +13312,20 @@
         <v>32</v>
       </c>
       <c r="E57" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F57" t="str">
         <f t="shared" si="1"/>
         <v>[Grau de Instrução]</v>
       </c>
       <c r="G57" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H57" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I57" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="J57" t="str">
         <f t="shared" ref="J57" si="6">"LEFT(CAST("&amp;H57&amp;"."&amp;I57&amp;" AS "&amp;G57&amp;"), "&amp;A57*1&amp;") AS "&amp;F57&amp;","</f>
@@ -13530,13 +13617,13 @@
         <v>[Nacionalidade (cfe. Tabela da Rais)]</v>
       </c>
       <c r="G70" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H70" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I70" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="J70" t="str">
         <f t="shared" ref="J70" si="9">"LEFT(CAST("&amp;H70&amp;"."&amp;I70&amp;" AS "&amp;G70&amp;"), "&amp;A70*1&amp;") AS "&amp;F70&amp;","</f>
@@ -13614,13 +13701,13 @@
         <v>[Certificado de Reservista]</v>
       </c>
       <c r="G73" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H73" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I73" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="J73" t="str">
         <f t="shared" ref="J73:J79" si="10">"LEFT(CAST("&amp;H73&amp;"."&amp;I73&amp;" AS "&amp;G73&amp;"), "&amp;A73*1&amp;") AS "&amp;F73&amp;","</f>
@@ -13648,13 +13735,13 @@
         <v>[Registro da Carteira de Habilitação]</v>
       </c>
       <c r="G74" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H74" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I74" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="J74" t="str">
         <f t="shared" si="10"/>
@@ -13682,13 +13769,13 @@
         <v>[Categoria da Carteira de Habilitação]</v>
       </c>
       <c r="G75" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H75" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I75" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="J75" t="str">
         <f t="shared" si="10"/>
@@ -13716,13 +13803,13 @@
         <v>[Data de Validade da Carteira de Habilitação]</v>
       </c>
       <c r="G76" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H76" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I76" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="J76" t="str">
         <f>"FORMAT("&amp;H76&amp;"."&amp;I76&amp;", 'ddMMyyyy') AS "&amp;F76&amp;","</f>
@@ -13750,13 +13837,13 @@
         <v>[Órgão Emissor da Carteira de Habilitação]</v>
       </c>
       <c r="G77" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H77" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I77" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="J77" t="str">
         <f t="shared" si="10"/>
@@ -13784,13 +13871,13 @@
         <v>[UF da Carteira de Habilitação]</v>
       </c>
       <c r="G78" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H78" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I78" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="J78" t="str">
         <f t="shared" si="10"/>
@@ -13818,13 +13905,13 @@
         <v>[Número do Cartão do SUS]</v>
       </c>
       <c r="G79" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H79" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I79" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="J79" t="str">
         <f t="shared" si="10"/>
@@ -13927,13 +14014,13 @@
         <v>[Número da Carteira de Trabalho]</v>
       </c>
       <c r="G83" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H83" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I83" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="J83" t="str">
         <f t="shared" ref="J83:J87" si="11">"LEFT(CAST("&amp;H83&amp;"."&amp;I83&amp;" AS "&amp;G83&amp;"), "&amp;A83*1&amp;") AS "&amp;F83&amp;","</f>
@@ -13961,13 +14048,13 @@
         <v>[Série da Carteira de Trabalho]</v>
       </c>
       <c r="G84" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H84" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I84" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="J84" t="str">
         <f t="shared" si="11"/>
@@ -13995,13 +14082,13 @@
         <v>[Data de Emissão da Carteira de Trabalho]</v>
       </c>
       <c r="G85" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H85" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I85" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="J85" t="str">
         <f>"FORMAT("&amp;H85&amp;"."&amp;I85&amp;", 'ddMMyyyy') AS "&amp;F85&amp;","</f>
@@ -14029,13 +14116,13 @@
         <v>[UF da Carteira de Trabalho]</v>
       </c>
       <c r="G86" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H86" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I86" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="J86" t="str">
         <f t="shared" si="11"/>
@@ -14063,13 +14150,13 @@
         <v>[Nome Completo]</v>
       </c>
       <c r="G87" t="s">
+        <v>325</v>
+      </c>
+      <c r="H87" t="s">
+        <v>806</v>
+      </c>
+      <c r="I87" t="s">
         <v>328</v>
-      </c>
-      <c r="H87" t="s">
-        <v>809</v>
-      </c>
-      <c r="I87" t="s">
-        <v>331</v>
       </c>
       <c r="J87" t="str">
         <f t="shared" si="11"/>
@@ -14097,13 +14184,13 @@
         <v>[Data de Expedição da Carteira de Habilitação]</v>
       </c>
       <c r="G88" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H88" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I88" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="J88" t="str">
         <f>"FORMAT("&amp;H88&amp;"."&amp;I88&amp;", 'ddMMyyyy') AS "&amp;F88&amp;","</f>
@@ -14151,19 +14238,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>324</v>
-      </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -14187,13 +14274,13 @@
         <v>[Código da Unidade, cfe. Tabela de Unidades]</v>
       </c>
       <c r="G2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I2" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J4" si="0">"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
@@ -14221,7 +14308,7 @@
         <v>[Código do Contrato]</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J6" si="1">"'' AS "&amp;F3&amp;","</f>
+        <f t="shared" ref="J2:J6" si="1">"'' AS "&amp;F3&amp;","</f>
         <v>'' AS [Código do Contrato],</v>
       </c>
     </row>
@@ -14239,20 +14326,20 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F4" t="str">
         <f>"["&amp;E4&amp;"]"</f>
         <v>[Data da Transferência]</v>
       </c>
       <c r="G4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H4" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I4" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="0"/>
@@ -14273,7 +14360,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F5" t="str">
         <f>"["&amp;E5&amp;"]"</f>
@@ -14298,7 +14385,7 @@
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F6" t="str">
         <f>"["&amp;E6&amp;"]"</f>
@@ -14348,22 +14435,22 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>324</v>
-      </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -14384,13 +14471,13 @@
         <v>[Código da Unidade, cfe. Tabela de Unidades]</v>
       </c>
       <c r="G2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J4" si="0">"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
@@ -14440,13 +14527,13 @@
         <v>[Data da Alteração]</v>
       </c>
       <c r="G4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="I4" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="0"/>
@@ -14464,7 +14551,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="1"/>
@@ -14629,13 +14716,13 @@
         <v>[Salário Contratual, cfe. Tipo de Salário]</v>
       </c>
       <c r="G13" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="H13" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I13" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" ref="J13:J14" si="3">"LEFT(CAST("&amp;H13&amp;"."&amp;I13&amp;" AS "&amp;G13&amp;"), "&amp;A13*1&amp;") AS "&amp;F13&amp;","</f>
@@ -14656,7 +14743,7 @@
         <v>8</v>
       </c>
       <c r="E14" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="1"/>
@@ -14664,13 +14751,13 @@
 de horistas (tipo de salário “5”).]</v>
       </c>
       <c r="G14" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="H14" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I14" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="3"/>
@@ -14696,7 +14783,7 @@
         <v>[Código do Cargo, cfe. Tabela de Cargos]</v>
       </c>
       <c r="G15" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="2"/>
@@ -14714,7 +14801,7 @@
         <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="1"/>
@@ -14736,7 +14823,7 @@
         <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="1"/>
@@ -14758,20 +14845,20 @@
         <v>8</v>
       </c>
       <c r="E18" t="s">
+        <v>796</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="1"/>
+        <v>[Salário Contratual Anterior (Se não houve alteração repita a informação atual) ]</v>
+      </c>
+      <c r="G18" t="s">
+        <v>332</v>
+      </c>
+      <c r="H18" t="s">
         <v>799</v>
       </c>
-      <c r="F18" t="str">
-        <f t="shared" si="1"/>
-        <v>[Salário Contratual Anterior (Se não houve alteração repita a informação atual) ]</v>
-      </c>
-      <c r="G18" t="s">
-        <v>335</v>
-      </c>
-      <c r="H18" t="s">
-        <v>802</v>
-      </c>
       <c r="I18" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" ref="J18:J19" si="4">"LEFT(CAST("&amp;H18&amp;"."&amp;I18&amp;" AS "&amp;G18&amp;"), "&amp;A18*1&amp;") AS "&amp;F18&amp;","</f>
@@ -14789,20 +14876,20 @@
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" si="1"/>
         <v>[Horas Contatuais Anterior (Se não houve alteração repita a informação atual) ]</v>
       </c>
       <c r="G19" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H19" t="s">
+        <v>799</v>
+      </c>
+      <c r="I19" t="s">
         <v>802</v>
-      </c>
-      <c r="I19" t="s">
-        <v>805</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="4"/>
@@ -14820,7 +14907,7 @@
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="1"/>
@@ -14872,19 +14959,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>324</v>
-      </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -14905,13 +14992,13 @@
         <v>[Código da Unidade, cfe. Tabela de Unidades]</v>
       </c>
       <c r="G2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="J2" t="str">
         <f>"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
@@ -14953,20 +15040,20 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
         <v>[Data de Início de Gozo das Férias]</v>
       </c>
       <c r="G4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" ref="J4:J9" si="2">"LEFT(CAST("&amp;H4&amp;"."&amp;I4&amp;" AS "&amp;G4&amp;"), "&amp;A4*1&amp;") AS "&amp;F4&amp;","</f>
@@ -14984,20 +15071,20 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="0"/>
         <v>[Data de Término de Gozo das Férias]</v>
       </c>
       <c r="G5" t="s">
+        <v>333</v>
+      </c>
+      <c r="H5" t="s">
+        <v>330</v>
+      </c>
+      <c r="I5" t="s">
         <v>336</v>
-      </c>
-      <c r="H5" t="s">
-        <v>333</v>
-      </c>
-      <c r="I5" t="s">
-        <v>339</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="2"/>
@@ -15015,20 +15102,20 @@
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" si="0"/>
         <v>[Data de Início do Período Aquisitivo]</v>
       </c>
       <c r="G6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="2"/>
@@ -15046,20 +15133,20 @@
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
         <v>[Data de Término do Período Aquisitivo]</v>
       </c>
       <c r="G7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="2"/>
@@ -15080,20 +15167,20 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
         <v>[Dias de Férias Cedidos]</v>
       </c>
       <c r="G8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="2"/>
@@ -15114,20 +15201,20 @@
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
         <v>[Dias de Abono Cedidos]</v>
       </c>
       <c r="G9" t="s">
+        <v>334</v>
+      </c>
+      <c r="H9" t="s">
+        <v>330</v>
+      </c>
+      <c r="I9" t="s">
         <v>337</v>
-      </c>
-      <c r="H9" t="s">
-        <v>333</v>
-      </c>
-      <c r="I9" t="s">
-        <v>340</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="2"/>
@@ -15177,19 +15264,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" t="s">
-        <v>324</v>
-      </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -15213,13 +15300,13 @@
         <v>[Código da Empresa, cfe. Tabela de Empresas]</v>
       </c>
       <c r="G2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="I2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="J2" t="str">
         <f>"LEFT(CAST("&amp;H2&amp;"."&amp;I2&amp;" AS "&amp;G2&amp;"), "&amp;A2*1&amp;") AS "&amp;F2&amp;","</f>
@@ -15247,13 +15334,13 @@
         <v>[Código da Pessoa]</v>
       </c>
       <c r="G3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="J3" t="str">
         <f>"LEFT(CAST("&amp;H3&amp;"."&amp;I3&amp;" AS "&amp;G3&amp;"), "&amp;A3*1&amp;") AS "&amp;F3&amp;","</f>
@@ -15274,20 +15361,20 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
         <v>[Familiar (Número Sequencial), iniciando em “01” a cada Pessoa]</v>
       </c>
       <c r="G4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H4" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="I4" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="J4" t="str">
         <f>"LEFT(CAST("&amp;H4&amp;"."&amp;I4&amp;" AS "&amp;G4&amp;"), "&amp;A4*1&amp;") AS "&amp;F4&amp;","</f>
@@ -15308,20 +15395,20 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="0"/>
         <v>[Nome do Familiar]</v>
       </c>
       <c r="G5" t="s">
+        <v>325</v>
+      </c>
+      <c r="H5" t="s">
+        <v>782</v>
+      </c>
+      <c r="I5" t="s">
         <v>328</v>
-      </c>
-      <c r="H5" t="s">
-        <v>785</v>
-      </c>
-      <c r="I5" t="s">
-        <v>331</v>
       </c>
       <c r="J5" t="str">
         <f>"LEFT(CAST("&amp;H5&amp;"."&amp;I5&amp;" AS "&amp;G5&amp;"), "&amp;A5*1&amp;") AS "&amp;F5&amp;","</f>
@@ -15349,13 +15436,13 @@
         <v>[Data de Nascimento]</v>
       </c>
       <c r="G6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="I6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="J6" t="str">
         <f>"LEFT(CAST("&amp;H6&amp;"."&amp;I6&amp;" AS "&amp;G6&amp;"), "&amp;A6*1&amp;") AS "&amp;F6&amp;","</f>
@@ -15376,7 +15463,7 @@
         <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
@@ -15429,16 +15516,16 @@
         <v>128</v>
       </c>
       <c r="F9" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H9" t="s">
+        <v>782</v>
+      </c>
+      <c r="I9" t="s">
         <v>785</v>
-      </c>
-      <c r="I9" t="s">
-        <v>788</v>
       </c>
       <c r="J9" t="str">
         <f>"LEFT(CAST("&amp;H9&amp;"."&amp;I9&amp;" AS "&amp;G9&amp;"), "&amp;A9*1&amp;") AS "&amp;F9&amp;","</f>
@@ -15487,20 +15574,20 @@
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" ref="F12" si="2">"["&amp;E12&amp;"]"</f>
         <v>[Grau de Parentesco:]</v>
       </c>
       <c r="G12" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H12" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="I12" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="J12" t="str">
         <f>"LEFT(CAST("&amp;H12&amp;"."&amp;I12&amp;" AS "&amp;G12&amp;"), "&amp;A12*1&amp;") AS "&amp;F12&amp;","</f>
@@ -15518,7 +15605,7 @@
         <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" ref="J13:J39" si="3">"'' AS "&amp;F13&amp;","</f>
@@ -15536,7 +15623,7 @@
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="3"/>
@@ -15554,7 +15641,7 @@
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="3"/>
@@ -15572,7 +15659,7 @@
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="3"/>
@@ -15590,7 +15677,7 @@
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="3"/>
@@ -15608,7 +15695,7 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="3"/>
@@ -15626,7 +15713,7 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="3"/>
@@ -15644,7 +15731,7 @@
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="3"/>
@@ -15662,7 +15749,7 @@
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="3"/>
@@ -15680,7 +15767,7 @@
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="3"/>
@@ -15698,7 +15785,7 @@
         <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="3"/>
@@ -15716,7 +15803,7 @@
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="3"/>
@@ -15734,7 +15821,7 @@
         <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
@@ -15755,7 +15842,7 @@
         <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F26" t="str">
         <f t="shared" ref="F26" si="4">"["&amp;E26&amp;"]"</f>
@@ -15777,7 +15864,7 @@
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J27" t="str">
         <f t="shared" si="3"/>
@@ -15795,7 +15882,7 @@
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="J28" t="str">
         <f t="shared" si="3"/>
@@ -15813,7 +15900,7 @@
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J29" t="str">
         <f t="shared" si="3"/>
@@ -15831,7 +15918,7 @@
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="J30" t="str">
         <f t="shared" si="3"/>
@@ -15849,7 +15936,7 @@
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J31" t="str">
         <f t="shared" si="3"/>
@@ -15867,7 +15954,7 @@
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="J32" t="str">
         <f t="shared" si="3"/>
@@ -15885,7 +15972,7 @@
         <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="J33" t="str">
         <f t="shared" si="3"/>
@@ -15906,20 +15993,20 @@
         <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F34" t="str">
         <f t="shared" ref="F34" si="5">"["&amp;E34&amp;"]"</f>
         <v>[Dependente para Salário Família:]</v>
       </c>
       <c r="G34" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H34" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="I34" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="J34" t="str">
         <f>"LEFT(CAST("&amp;H34&amp;"."&amp;I34&amp;" AS "&amp;G34&amp;"), "&amp;A34*1&amp;") AS "&amp;F34&amp;","</f>
@@ -15937,7 +16024,7 @@
         <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J35" t="str">
         <f t="shared" si="3"/>
@@ -15955,7 +16042,7 @@
         <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J36" t="str">
         <f t="shared" si="3"/>
@@ -15976,20 +16063,20 @@
         <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F37" t="str">
         <f t="shared" ref="F37" si="6">"["&amp;E37&amp;"]"</f>
         <v>[Dependente para o IRF:]</v>
       </c>
       <c r="G37" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H37" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="I37" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="J37" t="str">
         <f>"LEFT(CAST("&amp;H37&amp;"."&amp;I37&amp;" AS "&amp;G37&amp;"), "&amp;A37*1&amp;") AS "&amp;F37&amp;","</f>
@@ -16007,7 +16094,7 @@
         <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J38" t="str">
         <f t="shared" si="3"/>
@@ -16025,7 +16112,7 @@
         <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J39" t="str">
         <f t="shared" si="3"/>
@@ -16046,7 +16133,7 @@
         <v>8</v>
       </c>
       <c r="E40" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F40" t="str">
         <f t="shared" ref="F40" si="7">"["&amp;E40&amp;"]"</f>
@@ -16068,7 +16155,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
@@ -16082,7 +16169,7 @@
         <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -16099,7 +16186,7 @@
         <v>32</v>
       </c>
       <c r="E43" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F43" t="str">
         <f t="shared" ref="F43:F49" si="8">"["&amp;E43&amp;"]"</f>
@@ -16124,7 +16211,7 @@
         <v>32</v>
       </c>
       <c r="E44" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F44" t="str">
         <f t="shared" si="8"/>
@@ -16149,7 +16236,7 @@
         <v>32</v>
       </c>
       <c r="E45" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F45" t="str">
         <f t="shared" si="8"/>
@@ -16174,7 +16261,7 @@
         <v>32</v>
       </c>
       <c r="E46" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F46" t="str">
         <f t="shared" si="8"/>
@@ -16199,7 +16286,7 @@
         <v>32</v>
       </c>
       <c r="E47" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F47" t="str">
         <f t="shared" si="8"/>
@@ -16224,7 +16311,7 @@
         <v>32</v>
       </c>
       <c r="E48" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F48" t="str">
         <f t="shared" si="8"/>
@@ -16361,7 +16448,7 @@
         <v>7</v>
       </c>
       <c r="E55" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="J55" t="str">
         <f t="shared" si="9"/>
@@ -16379,7 +16466,7 @@
         <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J56" t="str">
         <f t="shared" si="9"/>
@@ -16397,7 +16484,7 @@
         <v>7</v>
       </c>
       <c r="E57" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="J57" t="str">
         <f t="shared" si="9"/>
@@ -16443,7 +16530,7 @@
         <v>32</v>
       </c>
       <c r="E59" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F59" t="str">
         <f t="shared" si="10"/>
@@ -16591,7 +16678,7 @@
         <v>7</v>
       </c>
       <c r="E67" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J67" t="str">
         <f t="shared" si="9"/>
@@ -16727,7 +16814,7 @@
         <v>32</v>
       </c>
       <c r="E74" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F74" t="str">
         <f t="shared" si="11"/>

--- a/DICIONARIO DE DADOS.xlsx
+++ b/DICIONARIO DE DADOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0-Repositorios\sql-migracao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66C104B-F1EF-4874-92E6-8EFB8440DEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68A760C-E4E5-49A4-AF1C-8F49DFDCE718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="920" xr2:uid="{365E4779-0F30-4366-ADA5-894CEE121BCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="920" firstSheet="1" activeTab="9" xr2:uid="{365E4779-0F30-4366-ADA5-894CEE121BCE}"/>
   </bookViews>
   <sheets>
     <sheet name="ALT CADASTRAIS" sheetId="12" r:id="rId1"/>
@@ -3754,7 +3754,13 @@
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E7FD2C1-E480-4BFF-8921-408BA731D000}" name="CONTRATO" displayName="CONTRATO" ref="A1:E144" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:E144" xr:uid="{6E7FD2C1-E480-4BFF-8921-408BA731D000}"/>
+  <autoFilter ref="A1:E144" xr:uid="{6E7FD2C1-E480-4BFF-8921-408BA731D000}">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{3C12D3CA-82E1-4D12-9D13-E5319871A469}" uniqueName="1" name="TM" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{05269625-8E6E-451A-95E7-F0B8439467BD}" uniqueName="2" name="F" queryTableFieldId="2" dataDxfId="7"/>
@@ -4448,7 +4454,7 @@
 alteração. Caso não seja informada, será gravada a atual.],</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4475,7 +4481,7 @@
 conversões para o Darwin.],</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>40</v>
       </c>
@@ -4748,7 +4754,7 @@
         <v>LEFT(CAST(PFUNC.CODSITUACAO AS VARCHAR), 1) AS [Situação:],</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -4767,7 +4773,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [1 – Ativo],</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -4786,7 +4792,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [2 – Afastado],</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>7</v>
       </c>
@@ -4805,7 +4811,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [3 – Rescindido no Mês],</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -4886,7 +4892,7 @@
         <v>LEFT(CAST(PFUNC.CODRECEBIMENTO AS VARCHAR), 1) AS [Tipo de Salário:],</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>7</v>
       </c>
@@ -4901,7 +4907,7 @@
         <v>[1 – Mensal]</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>7</v>
       </c>
@@ -4916,7 +4922,7 @@
         <v>[2 – Por Quinzena]</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>7</v>
       </c>
@@ -4931,7 +4937,7 @@
         <v>[3 – Por Semana]</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>7</v>
       </c>
@@ -4946,7 +4952,7 @@
         <v>[4 – Por Dia]</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>7</v>
       </c>
@@ -4961,7 +4967,7 @@
         <v>[5 – Por Hora]</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>7</v>
       </c>
@@ -4976,7 +4982,7 @@
         <v>[6 – Por Tarefa]</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>7</v>
       </c>
@@ -5115,7 +5121,7 @@
         <v>'' AS [Nível de Exposição a Agente Nocivo:],</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>7</v>
       </c>
@@ -5134,7 +5140,7 @@
         <v>'' AS [00 – Nunca esteve exposto],</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>7</v>
       </c>
@@ -5153,7 +5159,7 @@
         <v>'' AS [01 – Não exposto, mas já esteve],</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>7</v>
       </c>
@@ -5172,7 +5178,7 @@
         <v>'' AS [02 – Exposto com aposentadoria aos 15 anos],</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>7</v>
       </c>
@@ -5191,7 +5197,7 @@
         <v>'' AS [03 – Exposto com aposentadoria aos 20 anos],</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>7</v>
       </c>
@@ -5210,7 +5216,7 @@
         <v>'' AS [04 – Exposto com aposentadoria aos 25 anos],</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>7</v>
       </c>
@@ -5229,7 +5235,7 @@
         <v>'' AS [05 – Não exposto com mais de um vínculo],</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>7</v>
       </c>
@@ -5248,7 +5254,7 @@
         <v>'' AS [06 – Exposto c/aposentadoria 15 anos e mais de um vínculo],</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>7</v>
       </c>
@@ -5267,7 +5273,7 @@
         <v>'' AS [07 – Exposto c/aposentadoria 20 anos e mais de um vínculo],</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>7</v>
       </c>
@@ -5670,7 +5676,7 @@
         <v>2 AS [Tipo de Contrato],</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>7</v>
       </c>
@@ -5689,7 +5695,7 @@
         <v>'' AS [1 - Determinado],</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>7</v>
       </c>
@@ -5730,7 +5736,7 @@
         <v>'' AS [Motivo de Rescisão Darwin],</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>7</v>
       </c>
@@ -5745,7 +5751,7 @@
         <v>[001 – Demissão com Justa Causa]</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>7</v>
       </c>
@@ -5760,7 +5766,7 @@
         <v>[002 – Demissão Sem Justa Causa]</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>7</v>
       </c>
@@ -5775,7 +5781,7 @@
         <v>[003 – Pedido de Demissão Sem Justa Causa]</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>7</v>
       </c>
@@ -5790,7 +5796,7 @@
         <v>[005 – Rescisão Por Término de Contrato Prazo Determinado]</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>7</v>
       </c>
@@ -5805,7 +5811,7 @@
         <v>[006 – Resc. Ant. do Contr. Por Prazo Determinado p/Empregado]</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>7</v>
       </c>
@@ -5820,7 +5826,7 @@
         <v>[007 – Resc. Ant. do Contr. Por Prazo Determinado p/Empresa]</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>7</v>
       </c>
@@ -5835,7 +5841,7 @@
         <v>[008 – Rescisão p/Término de Contr. Temporário]</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>7</v>
       </c>
@@ -5850,7 +5856,7 @@
         <v>[009 – Rescisão por Dispensa Indireta]</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>7</v>
       </c>
@@ -5865,7 +5871,7 @@
         <v>[010 – Rescisão por Culpa Recíproca]</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>7</v>
       </c>
@@ -5880,7 +5886,7 @@
         <v>[011 – Transferência de Estab. c/Ônus p/Cedente]</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>7</v>
       </c>
@@ -5895,7 +5901,7 @@
         <v>[012 – Transferência de Estab. s/Ônus p/Cedente]</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>7</v>
       </c>
@@ -5910,7 +5916,7 @@
         <v>[013 – Mudança de Regime Trabalhista]</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>7</v>
       </c>
@@ -5925,7 +5931,7 @@
         <v>[014 – Reforma de Militar]</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>7</v>
       </c>
@@ -5940,7 +5946,7 @@
         <v>[015 – Demissão sem Justa Causa Empr. Doméstico]</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>7</v>
       </c>
@@ -5955,7 +5961,7 @@
         <v>[016 – Rescisão por Acordo Entre as Partes]</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>7</v>
       </c>
@@ -5970,7 +5976,7 @@
         <v>[017 – Desligamento p/Tranf. Outro Sistema]</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>7</v>
       </c>
@@ -5985,7 +5991,7 @@
         <v>[020 – Falecimento]</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>7</v>
       </c>
@@ -6000,7 +6006,7 @@
         <v>[021 – Falecimento Decorr. de Acidente do Trabalho]</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>7</v>
       </c>
@@ -6015,7 +6021,7 @@
         <v>[022 – Falecimento Decorr. de Doença Pr.]</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>7</v>
       </c>
@@ -6030,7 +6036,7 @@
         <v>[023 – Falecimento Decorr. de Acidente no Trajeto]</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>7</v>
       </c>
@@ -6045,7 +6051,7 @@
         <v>[030 – Aposentadoria por Tempo de Serviço]</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>7</v>
       </c>
@@ -6060,7 +6066,7 @@
         <v>[031 – Aposentadoria por Idade]</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>7</v>
       </c>
@@ -6075,7 +6081,7 @@
         <v>[032 – Aposentadoria por Invalidez]</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>7</v>
       </c>
@@ -6090,7 +6096,7 @@
         <v>[033 – Aposentadoria p/Invalidez Dec.Acid.Trab.]</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>7</v>
       </c>
@@ -6105,7 +6111,7 @@
         <v>[034 – Aposentadoria p/Invalidez Dec.Doença Pr.]</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>7</v>
       </c>
@@ -6120,7 +6126,7 @@
         <v>[035 - Aposentadoria Compulsória]</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>7</v>
       </c>
@@ -6135,7 +6141,7 @@
         <v>[036 - Aposentadoria Especial]</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>7</v>
       </c>
@@ -6150,7 +6156,7 @@
         <v>[037 - Termino de Contrato - Estagiário]</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>7</v>
       </c>
@@ -6165,7 +6171,7 @@
         <v>[040 - Posse em outro Cargo Inacumulável]</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>7</v>
       </c>
@@ -6180,7 +6186,7 @@
         <v>[041 - Rescisão determinada pela Justiça]</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>7</v>
       </c>
@@ -6195,7 +6201,7 @@
         <v>[043 - Rescisão por Nulidade do Contrato Trab.]</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>7</v>
       </c>
@@ -6210,7 +6216,7 @@
         <v>[044 - Exoneração Diretor Não Empreg. s/J Causa]</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>7</v>
       </c>
@@ -6225,7 +6231,7 @@
         <v>[045 - Término de Mandato do Diretor Não Empreg]</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>7</v>
       </c>
@@ -6240,7 +6246,7 @@
         <v>[046 - Exoneração a pedido de Diretor Não Empr.]</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>7</v>
       </c>
@@ -6255,7 +6261,7 @@
         <v>[047 - Exoneração Diretor Não Empreg. Culpa Rec]</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>7</v>
       </c>
@@ -6270,7 +6276,7 @@
         <v>[048 - Morte do Diretor Não Empregado]</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>7</v>
       </c>
@@ -6285,7 +6291,7 @@
         <v>[049 - Exoneração Diretor Não Empregado p/Falên]</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>7</v>
       </c>
@@ -6300,7 +6306,7 @@
         <v>[1401 - Aprendiz - Término de Contrato]</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>7</v>
       </c>
@@ -6315,7 +6321,7 @@
         <v>[1402 - Aprendiz - Implemento da Idade]</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>7</v>
       </c>
@@ -6330,7 +6336,7 @@
         <v>[1403 - Aprendiz - Desemp. Insuf. ou Inadaptação]</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>7</v>
       </c>
@@ -6345,7 +6351,7 @@
         <v>[1404 - Aprendiz - Falta Disciplinar Grave]</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>7</v>
       </c>
@@ -6360,7 +6366,7 @@
         <v>[1405 - Aprendiz - Ausência Injustific. à Escola]</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>7</v>
       </c>
@@ -6375,7 +6381,7 @@
         <v>[1406 - Aprendiz - A Pedido do Aprendiz]</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>7</v>
       </c>
@@ -6390,7 +6396,7 @@
         <v>[1407 - Aprendiz - Fechamento da Empresa]</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>7</v>
       </c>
@@ -6436,7 +6442,7 @@
         <v>LEFT(CAST(PFUNC.CODCATEGORIAESOCIAL AS VARCHAR), 8) AS [Vínculo Empregatício:],</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E99" t="s">
         <v>346</v>
       </c>
@@ -6449,7 +6455,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [001-CLT - Empregador Pessoa Jurídica, categoria e-Social 101 - Empregado],</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>7</v>
       </c>
@@ -6470,7 +6476,7 @@
 contratado pela CLT],</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>7</v>
       </c>
@@ -6489,7 +6495,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [002 -Aprendiz, categoria e-Social 103 - Empregado – Aprendiz],</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>7</v>
       </c>
@@ -6510,7 +6516,7 @@
 Contrato de trabalho intermitenteIntermitente,categoriae-Social111-Empregado-],</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>7</v>
       </c>
@@ -6529,7 +6535,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [004 -Estagiário, categoria e-Social 901 - Estagiário],</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>7</v>
       </c>
@@ -6548,7 +6554,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [006-TrabalhadorTemporário-Lei6.019,categoriae-Social106-],</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E105" t="s">
         <v>352</v>
       </c>
@@ -6561,7 +6567,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [Trabalhador Temporário - contrato nos termos da Lei 6.019/74],</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>7</v>
       </c>
@@ -6580,7 +6586,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [007-TrabalhadorTemporário-Lei9.601,categoriae-Social105-],</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E107" t="s">
         <v>354</v>
       </c>
@@ -6593,7 +6599,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [Empregado – contrato a termo firmado nos termos da Lei 9601/98],</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E108" t="s">
         <v>355</v>
       </c>
@@ -6606,7 +6612,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [008 - CLT - Prazo Determinado Fixo ou Obra Certa, categoria e-Social 101 -],</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>7</v>
       </c>
@@ -6627,7 +6633,7 @@
 ou indireta contratado pela CLT],</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E110" t="s">
         <v>357</v>
       </c>
@@ -6640,7 +6646,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [009 - Trabalhador Rural - Empregador Pessoa Jurídica, categoria e-Social],</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>7</v>
       </c>
@@ -6661,7 +6667,7 @@
 direta ou indireta contratado pela CLT],</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>7</v>
       </c>
@@ -6684,7 +6690,7 @@
 ou indireta contratado pela CLT],</v>
       </c>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>7</v>
       </c>
@@ -6707,7 +6713,7 @@
 - sem acordo para antecipação mensal da multa rescisória do FGTSdeTrabalhoVerdeeAmarelosemMultaFGTSMensal,],</v>
       </c>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>7</v>
       </c>
@@ -6730,7 +6736,7 @@
 - com acordo para antecipação mensal da multa rescisória do FGTSdeTrabalhoVerdeeAmarelocomMultaFGTSMensal,],</v>
       </c>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>7</v>
       </c>
@@ -6751,7 +6757,7 @@
 Avulso PortuárioAvulsoPortuário, categoria e-Social 201 -Trabalhador],</v>
       </c>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>7</v>
       </c>
@@ -6772,7 +6778,7 @@
 Trabalhador Avulso Não PortuárioAvulsoNãoPortuário,categoriae-Social202-],</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>7</v>
       </c>
@@ -6795,7 +6801,7 @@
 fiscal],</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>7</v>
       </c>
@@ -6814,7 +6820,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [102 - Diretor com FGTS - Sócio, categoria do e-Social 723 - Contribuinte],</v>
       </c>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E119" t="s">
         <v>366</v>
       </c>
@@ -6827,7 +6833,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [individual – empresários, sócios e membro de conselho de administração ou],</v>
       </c>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E120" t="s">
         <v>367</v>
       </c>
@@ -6840,7 +6846,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [fiscal],</v>
       </c>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>7</v>
       </c>
@@ -6859,7 +6865,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [103 - Diretor sem FGTS - Não Sócio, categoria e-social 722 - Contribuinte],</v>
       </c>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E122" t="s">
         <v>369</v>
       </c>
@@ -6872,7 +6878,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [individual – Diretor não empregado, sem FGTS],</v>
       </c>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>7</v>
       </c>
@@ -6891,7 +6897,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [104 - Diretor com FGTS - Não Sócio, categoria e-Social 721 - Contribuinte],</v>
       </c>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E124" t="s">
         <v>371</v>
       </c>
@@ -6904,7 +6910,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [individual – Diretor não empregado, com FGTS],</v>
       </c>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>7</v>
       </c>
@@ -6923,7 +6929,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [201-Autônomo,categoriae-Social701-Contribuinteindividual–],</v>
       </c>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E126" t="s">
         <v>373</v>
       </c>
@@ -6938,7 +6944,7 @@
 de contribuinte individual],</v>
       </c>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="E127" t="s">
         <v>374</v>
       </c>
@@ -6951,7 +6957,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [202-Freteiro-Carga,categoriae-Social712-Contribuinteindividual–],</v>
       </c>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>7</v>
       </c>
@@ -6970,7 +6976,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [Transportador autônomo de carga],</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>7</v>
       </c>
@@ -6991,7 +6997,7 @@
 – Transportador autônomo de passageiros],</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>7</v>
       </c>
@@ -7014,7 +7020,7 @@
 intermédio de Cooperativa de Trabalho],</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
         <v>7</v>
       </c>
@@ -7037,7 +7043,7 @@
 serviços por intermédio de cooperativa de trabalho],</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>7</v>
       </c>
@@ -7056,7 +7062,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [206 - Médico Residente, categoria e-Social 902 - Médico Residente],</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>7</v>
       </c>
@@ -7075,7 +7081,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [207 - MEI - Microempreendedor Individual, categoria e-Social 741 -Contribuinte individual - Microempreendedor Individual],</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
         <v>7</v>
       </c>
@@ -7094,7 +7100,7 @@
         <v>LEFT(CAST(. AS ), 0) AS [301 - Empregado(a) Doméstico(a), categoria e-Social 104 - Empregado-Doméstico],</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
         <v>7</v>
       </c>
@@ -7117,7 +7123,7 @@
 contratado pela CLT],</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
         <v>7</v>
       </c>
@@ -7138,7 +7144,7 @@
 uma das demais categorias de contribuinte individual],</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>7</v>
       </c>
@@ -7159,7 +7165,7 @@
 711 - Contribuinte individual – Transportador autônomo de passageiros],</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>7</v>
       </c>
@@ -7180,7 +7186,7 @@
 - Contribuinte individual – Transportador autônomo de carga],</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
         <v>7</v>
       </c>
@@ -7225,7 +7231,7 @@
         <v>'' AS [Tipo de Admissão para o eSocial],</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
         <v>7</v>
       </c>
@@ -7236,7 +7242,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
         <v>7</v>
       </c>
@@ -7247,7 +7253,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
         <v>7</v>
       </c>
@@ -7258,7 +7264,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>7</v>
       </c>
@@ -14308,7 +14314,7 @@
         <v>[Código do Contrato]</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J2:J6" si="1">"'' AS "&amp;F3&amp;","</f>
+        <f t="shared" ref="J3:J6" si="1">"'' AS "&amp;F3&amp;","</f>
         <v>'' AS [Código do Contrato],</v>
       </c>
     </row>
